--- a/templates/ERC000027/metadata_template_ERC000027.xlsx
+++ b/templates/ERC000027/metadata_template_ERC000027.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="environmentalpackage">'cv_sample'!$AI$1:$AI$1</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$M$1:$M$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$T$1:$T$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$O$1:$O$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AE$1:$AE$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="888">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1225,13 +1231,13 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>biomass</t>
   </si>
   <si>
-    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: t)</t>
+    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -1471,9 +1477,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1492,6 +1495,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1693,6 +1699,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1702,9 +1711,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1744,7 +1750,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1813,6 +1819,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1888,6 +1897,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1909,6 +1921,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1954,6 +1969,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1966,6 +1984,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1975,9 +1996,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2002,6 +2020,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2062,12 +2083,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2158,7 +2179,7 @@
     <t>water current</t>
   </si>
   <si>
-    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: m3/s)</t>
+    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: knot)</t>
   </si>
   <si>
     <t>fluorescence</t>
@@ -2200,7 +2221,7 @@
     <t>pressure</t>
   </si>
   <si>
-    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: bar)</t>
+    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: atm)</t>
   </si>
   <si>
     <t>high</t>
@@ -2272,7 +2293,7 @@
     <t>bishomohopanol</t>
   </si>
   <si>
-    <t>(Optional) Concentration of bishomohopanol (Units: µg/g)</t>
+    <t>(Optional) Concentration of bishomohopanol (Units: µg/L)</t>
   </si>
   <si>
     <t>bromide</t>
@@ -2284,7 +2305,7 @@
     <t>calcium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of calcium (Units: µmol/L)</t>
+    <t>(Optional) Concentration of calcium (Units: mg/L)</t>
   </si>
   <si>
     <t>carbon/nitrogen ratio</t>
@@ -2368,7 +2389,7 @@
     <t>magnesium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of magnesium (Units: parts/million)</t>
+    <t>(Optional) Concentration of magnesium (Units: mg/L)</t>
   </si>
   <si>
     <t>n-alkanes</t>
@@ -2458,7 +2479,7 @@
     <t>primary production</t>
   </si>
   <si>
-    <t>(Optional) Measurement of primary production (Units: mg/m3/day)</t>
+    <t>(Optional) Measurement of primary production (Units: g/m2/day)</t>
   </si>
   <si>
     <t>redox potential</t>
@@ -2494,13 +2515,13 @@
     <t>sulfate</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfate (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfate (Units: mg/L)</t>
   </si>
   <si>
     <t>sulfide</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfide (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfide (Units: mg/L)</t>
   </si>
   <si>
     <t>suspended particulate matter</t>
@@ -2524,13 +2545,13 @@
     <t>total nitrogen content</t>
   </si>
   <si>
-    <t>(Optional) Total nitrogen content of the sample (Units: µmol/L)</t>
+    <t>(Optional) Total nitrogen content of the sample (Units: µg/L)</t>
   </si>
   <si>
     <t>total particulate carbon</t>
   </si>
   <si>
-    <t>(Optional) Total particulate carbon content (Units: µmol/L)</t>
+    <t>(Optional) Total particulate carbon content (Units: µg/L)</t>
   </si>
   <si>
     <t>total phosphorus</t>
@@ -2608,7 +2629,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -2674,7 +2695,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>chemical administration</t>
@@ -3207,10 +3228,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3251,10 +3272,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3281,7 +3302,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3298,7 +3319,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3315,7 +3336,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3332,7 +3353,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3349,7 +3370,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3366,7 +3387,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3383,7 +3404,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3400,7 +3421,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3417,7 +3438,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3434,7 +3455,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3448,7 +3469,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3462,7 +3483,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3476,7 +3497,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3490,7 +3511,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3504,7 +3525,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3518,7 +3539,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3532,7 +3553,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3546,7 +3567,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3556,8 +3577,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3568,7 +3592,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3579,7 +3603,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3590,7 +3614,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3601,7 +3625,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3612,7 +3636,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3623,7 +3647,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3634,7 +3658,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3645,7 +3669,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3656,7 +3680,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3667,7 +3691,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3678,7 +3702,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3689,7 +3713,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3700,7 +3724,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3708,7 +3732,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3716,7 +3740,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3724,7 +3748,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3732,7 +3756,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3740,7 +3764,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3748,7 +3772,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3756,7 +3780,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3764,7 +3788,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3772,7 +3796,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3780,236 +3804,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4031,27 +4060,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4071,122 +4100,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4210,840 +4239,840 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:140" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -5079,1602 +5108,1627 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="L1:BJ289"/>
+  <dimension ref="L1:BJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="12:62">
       <c r="L1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AI1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AW1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BJ1" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="2" spans="12:62">
       <c r="L2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AE2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AW2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BJ2" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="12:62">
       <c r="L3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AE3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AW3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="12:62">
       <c r="L4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AW4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="12:62">
       <c r="L5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AW5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="12:62">
       <c r="L6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AW6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="12:62">
       <c r="L7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AW7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="12:62">
       <c r="L8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AW8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="12:62">
       <c r="L9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AW9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="12:62">
       <c r="L10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AW10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="12:62">
       <c r="L11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AW11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="12:62">
       <c r="L12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AW12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="12:62">
       <c r="L13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AW13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="12:62">
       <c r="L14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AW14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="12:62">
       <c r="L15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AW15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="12:62">
       <c r="L16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AW16" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="12:49">
       <c r="L17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AW17" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="12:49">
       <c r="L18" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AW18" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="12:49">
       <c r="L19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AW19" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="12:49">
       <c r="L20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AW20" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="12:49">
       <c r="L21" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AW21" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="12:49">
       <c r="L22" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AW22" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="12:49">
       <c r="L23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AW23" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="12:49">
       <c r="L24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AW24" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="12:49">
       <c r="L25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AW25" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="12:49">
       <c r="L26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AW26" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="12:49">
       <c r="L27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AW27" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="12:49">
       <c r="L28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AW28" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="12:49">
       <c r="L29" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AW29" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="12:49">
       <c r="L30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AW30" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="12:49">
       <c r="AW31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="12:49">
       <c r="AW32" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" spans="49:49">
       <c r="AW33" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="49:49">
       <c r="AW34" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" spans="49:49">
       <c r="AW35" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="49:49">
       <c r="AW36" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="49:49">
       <c r="AW37" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" spans="49:49">
       <c r="AW38" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" spans="49:49">
       <c r="AW39" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="49:49">
       <c r="AW40" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="49:49">
       <c r="AW41" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42" spans="49:49">
       <c r="AW42" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" spans="49:49">
       <c r="AW43" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="49:49">
       <c r="AW44" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="49:49">
       <c r="AW45" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="49:49">
       <c r="AW46" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47" spans="49:49">
       <c r="AW47" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="48" spans="49:49">
       <c r="AW48" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="49" spans="49:49">
       <c r="AW49" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="50" spans="49:49">
       <c r="AW50" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="51" spans="49:49">
       <c r="AW51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="52" spans="49:49">
       <c r="AW52" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="53" spans="49:49">
       <c r="AW53" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="49:49">
       <c r="AW54" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="55" spans="49:49">
       <c r="AW55" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="56" spans="49:49">
       <c r="AW56" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57" spans="49:49">
       <c r="AW57" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="49:49">
       <c r="AW58" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="59" spans="49:49">
       <c r="AW59" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="60" spans="49:49">
       <c r="AW60" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61" spans="49:49">
       <c r="AW61" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" spans="49:49">
       <c r="AW62" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="63" spans="49:49">
       <c r="AW63" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" spans="49:49">
       <c r="AW64" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="49:49">
       <c r="AW65" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="66" spans="49:49">
       <c r="AW66" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="67" spans="49:49">
       <c r="AW67" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" spans="49:49">
       <c r="AW68" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="69" spans="49:49">
       <c r="AW69" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70" spans="49:49">
       <c r="AW70" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="71" spans="49:49">
       <c r="AW71" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" spans="49:49">
       <c r="AW72" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" spans="49:49">
       <c r="AW73" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74" spans="49:49">
       <c r="AW74" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="75" spans="49:49">
       <c r="AW75" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="76" spans="49:49">
       <c r="AW76" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="77" spans="49:49">
       <c r="AW77" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="78" spans="49:49">
       <c r="AW78" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="79" spans="49:49">
       <c r="AW79" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" spans="49:49">
       <c r="AW80" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" spans="49:49">
       <c r="AW81" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="49:49">
       <c r="AW82" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="83" spans="49:49">
       <c r="AW83" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="84" spans="49:49">
       <c r="AW84" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="85" spans="49:49">
       <c r="AW85" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="86" spans="49:49">
       <c r="AW86" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="87" spans="49:49">
       <c r="AW87" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="88" spans="49:49">
       <c r="AW88" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="89" spans="49:49">
       <c r="AW89" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="90" spans="49:49">
       <c r="AW90" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="91" spans="49:49">
       <c r="AW91" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92" spans="49:49">
       <c r="AW92" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" spans="49:49">
       <c r="AW93" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="49:49">
       <c r="AW94" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" spans="49:49">
       <c r="AW95" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96" spans="49:49">
       <c r="AW96" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="97" spans="49:49">
       <c r="AW97" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="98" spans="49:49">
       <c r="AW98" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="99" spans="49:49">
       <c r="AW99" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="49:49">
       <c r="AW100" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="101" spans="49:49">
       <c r="AW101" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="102" spans="49:49">
       <c r="AW102" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="103" spans="49:49">
       <c r="AW103" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="104" spans="49:49">
       <c r="AW104" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="105" spans="49:49">
       <c r="AW105" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="106" spans="49:49">
       <c r="AW106" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="107" spans="49:49">
       <c r="AW107" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="108" spans="49:49">
       <c r="AW108" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="109" spans="49:49">
       <c r="AW109" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="110" spans="49:49">
       <c r="AW110" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="111" spans="49:49">
       <c r="AW111" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="112" spans="49:49">
       <c r="AW112" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="113" spans="49:49">
       <c r="AW113" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="114" spans="49:49">
       <c r="AW114" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="115" spans="49:49">
       <c r="AW115" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="116" spans="49:49">
       <c r="AW116" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="117" spans="49:49">
       <c r="AW117" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="118" spans="49:49">
       <c r="AW118" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="119" spans="49:49">
       <c r="AW119" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="120" spans="49:49">
       <c r="AW120" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="121" spans="49:49">
       <c r="AW121" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="122" spans="49:49">
       <c r="AW122" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="123" spans="49:49">
       <c r="AW123" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="124" spans="49:49">
       <c r="AW124" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="125" spans="49:49">
       <c r="AW125" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="126" spans="49:49">
       <c r="AW126" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="127" spans="49:49">
       <c r="AW127" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="128" spans="49:49">
       <c r="AW128" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="129" spans="49:49">
       <c r="AW129" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="130" spans="49:49">
       <c r="AW130" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="131" spans="49:49">
       <c r="AW131" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="132" spans="49:49">
       <c r="AW132" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="133" spans="49:49">
       <c r="AW133" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="134" spans="49:49">
       <c r="AW134" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="135" spans="49:49">
       <c r="AW135" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="136" spans="49:49">
       <c r="AW136" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="137" spans="49:49">
       <c r="AW137" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="138" spans="49:49">
       <c r="AW138" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="49:49">
       <c r="AW139" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="140" spans="49:49">
       <c r="AW140" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="141" spans="49:49">
       <c r="AW141" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="142" spans="49:49">
       <c r="AW142" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="143" spans="49:49">
       <c r="AW143" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="144" spans="49:49">
       <c r="AW144" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="145" spans="49:49">
       <c r="AW145" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="146" spans="49:49">
       <c r="AW146" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="147" spans="49:49">
       <c r="AW147" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="148" spans="49:49">
       <c r="AW148" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="149" spans="49:49">
       <c r="AW149" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="150" spans="49:49">
       <c r="AW150" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="151" spans="49:49">
       <c r="AW151" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="152" spans="49:49">
       <c r="AW152" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="153" spans="49:49">
       <c r="AW153" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="154" spans="49:49">
       <c r="AW154" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="155" spans="49:49">
       <c r="AW155" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="156" spans="49:49">
       <c r="AW156" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="157" spans="49:49">
       <c r="AW157" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="158" spans="49:49">
       <c r="AW158" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="159" spans="49:49">
       <c r="AW159" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="160" spans="49:49">
       <c r="AW160" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="161" spans="49:49">
       <c r="AW161" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="162" spans="49:49">
       <c r="AW162" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="163" spans="49:49">
       <c r="AW163" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="164" spans="49:49">
       <c r="AW164" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="165" spans="49:49">
       <c r="AW165" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="166" spans="49:49">
       <c r="AW166" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="167" spans="49:49">
       <c r="AW167" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="168" spans="49:49">
       <c r="AW168" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="169" spans="49:49">
       <c r="AW169" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="170" spans="49:49">
       <c r="AW170" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="171" spans="49:49">
       <c r="AW171" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="172" spans="49:49">
       <c r="AW172" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="173" spans="49:49">
       <c r="AW173" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="174" spans="49:49">
       <c r="AW174" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="175" spans="49:49">
       <c r="AW175" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="176" spans="49:49">
       <c r="AW176" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="177" spans="49:49">
       <c r="AW177" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="178" spans="49:49">
       <c r="AW178" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="179" spans="49:49">
       <c r="AW179" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="180" spans="49:49">
       <c r="AW180" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="181" spans="49:49">
       <c r="AW181" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="182" spans="49:49">
       <c r="AW182" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="183" spans="49:49">
       <c r="AW183" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="184" spans="49:49">
       <c r="AW184" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="185" spans="49:49">
       <c r="AW185" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="186" spans="49:49">
       <c r="AW186" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="187" spans="49:49">
       <c r="AW187" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="188" spans="49:49">
       <c r="AW188" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="189" spans="49:49">
       <c r="AW189" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="190" spans="49:49">
       <c r="AW190" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="191" spans="49:49">
       <c r="AW191" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="192" spans="49:49">
       <c r="AW192" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="193" spans="49:49">
       <c r="AW193" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="194" spans="49:49">
       <c r="AW194" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="195" spans="49:49">
       <c r="AW195" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="196" spans="49:49">
       <c r="AW196" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="197" spans="49:49">
       <c r="AW197" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="198" spans="49:49">
       <c r="AW198" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="199" spans="49:49">
       <c r="AW199" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="200" spans="49:49">
       <c r="AW200" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="201" spans="49:49">
       <c r="AW201" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="202" spans="49:49">
       <c r="AW202" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="203" spans="49:49">
       <c r="AW203" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="204" spans="49:49">
       <c r="AW204" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="205" spans="49:49">
       <c r="AW205" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="206" spans="49:49">
       <c r="AW206" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="207" spans="49:49">
       <c r="AW207" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="208" spans="49:49">
       <c r="AW208" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="209" spans="49:49">
       <c r="AW209" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="210" spans="49:49">
       <c r="AW210" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="211" spans="49:49">
       <c r="AW211" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="212" spans="49:49">
       <c r="AW212" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="213" spans="49:49">
       <c r="AW213" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="214" spans="49:49">
       <c r="AW214" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="215" spans="49:49">
       <c r="AW215" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="216" spans="49:49">
       <c r="AW216" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="217" spans="49:49">
       <c r="AW217" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="218" spans="49:49">
       <c r="AW218" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="219" spans="49:49">
       <c r="AW219" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="220" spans="49:49">
       <c r="AW220" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="221" spans="49:49">
       <c r="AW221" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="222" spans="49:49">
       <c r="AW222" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="223" spans="49:49">
       <c r="AW223" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="224" spans="49:49">
       <c r="AW224" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="225" spans="49:49">
       <c r="AW225" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="226" spans="49:49">
       <c r="AW226" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="227" spans="49:49">
       <c r="AW227" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="228" spans="49:49">
       <c r="AW228" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="229" spans="49:49">
       <c r="AW229" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="230" spans="49:49">
       <c r="AW230" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="231" spans="49:49">
       <c r="AW231" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="232" spans="49:49">
       <c r="AW232" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="233" spans="49:49">
       <c r="AW233" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="234" spans="49:49">
       <c r="AW234" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="235" spans="49:49">
       <c r="AW235" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="236" spans="49:49">
       <c r="AW236" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="237" spans="49:49">
       <c r="AW237" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="238" spans="49:49">
       <c r="AW238" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="239" spans="49:49">
       <c r="AW239" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="240" spans="49:49">
       <c r="AW240" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="241" spans="49:49">
       <c r="AW241" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="242" spans="49:49">
       <c r="AW242" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="243" spans="49:49">
       <c r="AW243" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="244" spans="49:49">
       <c r="AW244" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="245" spans="49:49">
       <c r="AW245" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="246" spans="49:49">
       <c r="AW246" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="247" spans="49:49">
       <c r="AW247" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="248" spans="49:49">
       <c r="AW248" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="249" spans="49:49">
       <c r="AW249" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="250" spans="49:49">
       <c r="AW250" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="251" spans="49:49">
       <c r="AW251" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="252" spans="49:49">
       <c r="AW252" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="253" spans="49:49">
       <c r="AW253" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="254" spans="49:49">
       <c r="AW254" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="255" spans="49:49">
       <c r="AW255" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="256" spans="49:49">
       <c r="AW256" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="257" spans="49:49">
       <c r="AW257" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="258" spans="49:49">
       <c r="AW258" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="259" spans="49:49">
       <c r="AW259" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="260" spans="49:49">
       <c r="AW260" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="261" spans="49:49">
       <c r="AW261" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="262" spans="49:49">
       <c r="AW262" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="263" spans="49:49">
       <c r="AW263" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="264" spans="49:49">
       <c r="AW264" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="265" spans="49:49">
       <c r="AW265" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="266" spans="49:49">
       <c r="AW266" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="267" spans="49:49">
       <c r="AW267" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="268" spans="49:49">
       <c r="AW268" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="269" spans="49:49">
       <c r="AW269" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="270" spans="49:49">
       <c r="AW270" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="271" spans="49:49">
       <c r="AW271" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="272" spans="49:49">
       <c r="AW272" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="273" spans="49:49">
       <c r="AW273" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="274" spans="49:49">
       <c r="AW274" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="275" spans="49:49">
       <c r="AW275" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="276" spans="49:49">
       <c r="AW276" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="277" spans="49:49">
       <c r="AW277" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="278" spans="49:49">
       <c r="AW278" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="279" spans="49:49">
       <c r="AW279" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="280" spans="49:49">
       <c r="AW280" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="281" spans="49:49">
       <c r="AW281" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="282" spans="49:49">
       <c r="AW282" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="283" spans="49:49">
       <c r="AW283" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="284" spans="49:49">
       <c r="AW284" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="285" spans="49:49">
       <c r="AW285" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="286" spans="49:49">
       <c r="AW286" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="287" spans="49:49">
       <c r="AW287" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="288" spans="49:49">
       <c r="AW288" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="289" spans="49:49">
       <c r="AW289" t="s">
-        <v>694</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="290" spans="49:49">
+      <c r="AW290" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="291" spans="49:49">
+      <c r="AW291" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="292" spans="49:49">
+      <c r="AW292" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="293" spans="49:49">
+      <c r="AW293" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="294" spans="49:49">
+      <c r="AW294" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000027/metadata_template_ERC000027.xlsx
+++ b/templates/ERC000027/metadata_template_ERC000027.xlsx
@@ -17,28 +17,28 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="environmentalpackage">'cv_sample'!$AG$1:$AG$1</definedName>
+    <definedName name="environmentalpackage">'cv_sample'!$AH$1:$AH$1</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AU$1:$AU$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AV$1:$AV$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$K$1:$K$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$R$1:$R$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$M$1:$M$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AC$1:$AC$3</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$L$1:$L$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$S$1:$S$2</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$N$1:$N$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AD$1:$AD$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="tidalstage">'cv_sample'!$BH$1:$BH$2</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$J$1:$J$30</definedName>
+    <definedName name="tidalstage">'cv_sample'!$BI$1:$BI$2</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$K$1:$K$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="886">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -844,6 +850,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1459,9 +1471,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1480,6 +1489,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1681,6 +1693,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1690,9 +1705,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1732,7 +1744,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1801,6 +1813,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1876,6 +1891,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1897,6 +1915,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1942,6 +1963,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1954,6 +1978,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1963,9 +1990,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1990,6 +2014,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2050,10 +2077,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3195,10 +3222,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3239,10 +3266,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3269,7 +3296,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3286,7 +3313,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3303,7 +3330,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3320,7 +3347,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3337,7 +3364,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3354,7 +3381,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3371,7 +3398,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3388,7 +3415,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3405,7 +3432,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3422,7 +3449,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3436,7 +3463,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3450,7 +3477,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3464,7 +3491,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3478,7 +3505,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3492,7 +3519,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3506,7 +3533,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3520,7 +3547,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3534,7 +3561,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3544,8 +3571,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3556,7 +3586,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3567,7 +3597,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3578,7 +3608,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3589,7 +3619,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3600,7 +3630,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3611,7 +3641,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3622,7 +3652,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3633,7 +3663,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3644,7 +3674,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3655,7 +3685,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3666,7 +3696,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3677,7 +3707,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3688,7 +3718,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3696,7 +3726,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3704,7 +3734,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3712,7 +3742,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3720,7 +3750,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3728,7 +3758,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3736,7 +3766,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3744,7 +3774,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3752,7 +3782,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3760,7 +3790,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3768,236 +3798,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4019,27 +4054,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4059,122 +4094,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4184,13 +4219,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EH2"/>
+  <dimension ref="A1:EI2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:138">
+    <row r="1" spans="1:139">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4198,854 +4233,860 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>691</v>
+        <v>404</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="2" spans="1:138" ht="150" customHeight="1">
+        <v>882</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="2" spans="1:139" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>692</v>
+        <v>405</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
+      </c>
+      <c r="EI2" s="2" t="s">
+        <v>885</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG3:AG101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3:AH101">
       <formula1>environmentalpackage</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU3:AU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH3:BH101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI101">
       <formula1>tidalstage</formula1>
     </dataValidation>
   </dataValidations>
@@ -5055,1602 +5096,1627 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="J1:BH289"/>
+  <dimension ref="K1:BI294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="10:60">
-      <c r="J1" t="s">
-        <v>280</v>
-      </c>
+    <row r="1" spans="11:61">
       <c r="K1" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1" t="s">
+        <v>316</v>
+      </c>
+      <c r="N1" t="s">
+        <v>325</v>
+      </c>
+      <c r="S1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>377</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>406</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="2" spans="11:61">
+      <c r="K2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L2" t="s">
+        <v>317</v>
+      </c>
+      <c r="N2" t="s">
+        <v>326</v>
+      </c>
+      <c r="S2" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>367</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>407</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="3" spans="11:61">
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="L3" t="s">
+        <v>318</v>
+      </c>
+      <c r="N3" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>368</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" spans="11:61">
+      <c r="K4" t="s">
+        <v>287</v>
+      </c>
+      <c r="L4" t="s">
+        <v>319</v>
+      </c>
+      <c r="N4" t="s">
+        <v>328</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="11:61">
+      <c r="K5" t="s">
+        <v>288</v>
+      </c>
+      <c r="L5" t="s">
+        <v>320</v>
+      </c>
+      <c r="N5" t="s">
+        <v>329</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="6" spans="11:61">
+      <c r="K6" t="s">
+        <v>289</v>
+      </c>
+      <c r="N6" t="s">
+        <v>330</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="11:61">
+      <c r="K7" t="s">
+        <v>290</v>
+      </c>
+      <c r="N7" t="s">
+        <v>331</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="11:61">
+      <c r="K8" t="s">
+        <v>291</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="9" spans="11:61">
+      <c r="K9" t="s">
+        <v>292</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="11:61">
+      <c r="K10" t="s">
+        <v>293</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="11" spans="11:61">
+      <c r="K11" t="s">
+        <v>294</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="11:61">
+      <c r="K12" t="s">
+        <v>295</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="13" spans="11:61">
+      <c r="K13" t="s">
+        <v>296</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="14" spans="11:61">
+      <c r="K14" t="s">
+        <v>297</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="15" spans="11:61">
+      <c r="K15" t="s">
+        <v>298</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="11:61">
+      <c r="K16" t="s">
+        <v>299</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="11:48">
+      <c r="K17" t="s">
+        <v>300</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="18" spans="11:48">
+      <c r="K18" t="s">
+        <v>301</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="19" spans="11:48">
+      <c r="K19" t="s">
+        <v>302</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="20" spans="11:48">
+      <c r="K20" t="s">
+        <v>303</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="21" spans="11:48">
+      <c r="K21" t="s">
+        <v>304</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="22" spans="11:48">
+      <c r="K22" t="s">
+        <v>305</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="23" spans="11:48">
+      <c r="K23" t="s">
+        <v>306</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="11:48">
+      <c r="K24" t="s">
+        <v>307</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="25" spans="11:48">
+      <c r="K25" t="s">
+        <v>308</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="11:48">
+      <c r="K26" t="s">
+        <v>309</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" spans="11:48">
+      <c r="K27" t="s">
+        <v>310</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="28" spans="11:48">
+      <c r="K28" t="s">
+        <v>311</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="11:48">
+      <c r="K29" t="s">
         <v>312</v>
       </c>
-      <c r="M1" t="s">
-        <v>321</v>
-      </c>
-      <c r="R1" t="s">
-        <v>338</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>362</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>373</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>402</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="2" spans="10:60">
-      <c r="J2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="AV29" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="30" spans="11:48">
+      <c r="K30" t="s">
         <v>313</v>
       </c>
-      <c r="M2" t="s">
-        <v>322</v>
-      </c>
-      <c r="R2" t="s">
-        <v>339</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>363</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>403</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="3" spans="10:60">
-      <c r="J3" t="s">
-        <v>282</v>
-      </c>
-      <c r="K3" t="s">
-        <v>314</v>
-      </c>
-      <c r="M3" t="s">
-        <v>323</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>364</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="4" spans="10:60">
-      <c r="J4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K4" t="s">
-        <v>315</v>
-      </c>
-      <c r="M4" t="s">
-        <v>324</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="5" spans="10:60">
-      <c r="J5" t="s">
-        <v>284</v>
-      </c>
-      <c r="K5" t="s">
-        <v>316</v>
-      </c>
-      <c r="M5" t="s">
-        <v>325</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="6" spans="10:60">
-      <c r="J6" t="s">
-        <v>285</v>
-      </c>
-      <c r="M6" t="s">
-        <v>326</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="7" spans="10:60">
-      <c r="J7" t="s">
-        <v>286</v>
-      </c>
-      <c r="M7" t="s">
-        <v>327</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8" spans="10:60">
-      <c r="J8" t="s">
-        <v>287</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="9" spans="10:60">
-      <c r="J9" t="s">
-        <v>288</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10" spans="10:60">
-      <c r="J10" t="s">
-        <v>289</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="11" spans="10:60">
-      <c r="J11" t="s">
-        <v>290</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="12" spans="10:60">
-      <c r="J12" t="s">
-        <v>291</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="13" spans="10:60">
-      <c r="J13" t="s">
-        <v>292</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="14" spans="10:60">
-      <c r="J14" t="s">
-        <v>293</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="15" spans="10:60">
-      <c r="J15" t="s">
-        <v>294</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="16" spans="10:60">
-      <c r="J16" t="s">
-        <v>295</v>
-      </c>
-      <c r="AU16" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="17" spans="10:47">
-      <c r="J17" t="s">
-        <v>296</v>
-      </c>
-      <c r="AU17" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="18" spans="10:47">
-      <c r="J18" t="s">
-        <v>297</v>
-      </c>
-      <c r="AU18" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="19" spans="10:47">
-      <c r="J19" t="s">
-        <v>298</v>
-      </c>
-      <c r="AU19" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="20" spans="10:47">
-      <c r="J20" t="s">
-        <v>299</v>
-      </c>
-      <c r="AU20" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="21" spans="10:47">
-      <c r="J21" t="s">
-        <v>300</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="22" spans="10:47">
-      <c r="J22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AU22" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="23" spans="10:47">
-      <c r="J23" t="s">
-        <v>302</v>
-      </c>
-      <c r="AU23" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="24" spans="10:47">
-      <c r="J24" t="s">
-        <v>303</v>
-      </c>
-      <c r="AU24" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="25" spans="10:47">
-      <c r="J25" t="s">
-        <v>304</v>
-      </c>
-      <c r="AU25" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="26" spans="10:47">
-      <c r="J26" t="s">
-        <v>305</v>
-      </c>
-      <c r="AU26" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="27" spans="10:47">
-      <c r="J27" t="s">
-        <v>306</v>
-      </c>
-      <c r="AU27" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="28" spans="10:47">
-      <c r="J28" t="s">
-        <v>307</v>
-      </c>
-      <c r="AU28" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="29" spans="10:47">
-      <c r="J29" t="s">
-        <v>308</v>
-      </c>
-      <c r="AU29" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="30" spans="10:47">
-      <c r="J30" t="s">
-        <v>309</v>
-      </c>
-      <c r="AU30" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="31" spans="10:47">
-      <c r="AU31" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="32" spans="10:47">
-      <c r="AU32" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="33" spans="47:47">
-      <c r="AU33" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="34" spans="47:47">
-      <c r="AU34" t="s">
+      <c r="AV30" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="35" spans="47:47">
-      <c r="AU35" t="s">
+    <row r="31" spans="11:48">
+      <c r="AV31" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="36" spans="47:47">
-      <c r="AU36" t="s">
+    <row r="32" spans="11:48">
+      <c r="AV32" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="37" spans="47:47">
-      <c r="AU37" t="s">
+    <row r="33" spans="48:48">
+      <c r="AV33" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="38" spans="47:47">
-      <c r="AU38" t="s">
+    <row r="34" spans="48:48">
+      <c r="AV34" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="39" spans="47:47">
-      <c r="AU39" t="s">
+    <row r="35" spans="48:48">
+      <c r="AV35" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="40" spans="47:47">
-      <c r="AU40" t="s">
+    <row r="36" spans="48:48">
+      <c r="AV36" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="41" spans="47:47">
-      <c r="AU41" t="s">
+    <row r="37" spans="48:48">
+      <c r="AV37" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="42" spans="47:47">
-      <c r="AU42" t="s">
+    <row r="38" spans="48:48">
+      <c r="AV38" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="43" spans="47:47">
-      <c r="AU43" t="s">
+    <row r="39" spans="48:48">
+      <c r="AV39" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="44" spans="47:47">
-      <c r="AU44" t="s">
+    <row r="40" spans="48:48">
+      <c r="AV40" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="45" spans="47:47">
-      <c r="AU45" t="s">
+    <row r="41" spans="48:48">
+      <c r="AV41" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="46" spans="47:47">
-      <c r="AU46" t="s">
+    <row r="42" spans="48:48">
+      <c r="AV42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="47" spans="47:47">
-      <c r="AU47" t="s">
+    <row r="43" spans="48:48">
+      <c r="AV43" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="48" spans="47:47">
-      <c r="AU48" t="s">
+    <row r="44" spans="48:48">
+      <c r="AV44" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="49" spans="47:47">
-      <c r="AU49" t="s">
+    <row r="45" spans="48:48">
+      <c r="AV45" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="50" spans="47:47">
-      <c r="AU50" t="s">
+    <row r="46" spans="48:48">
+      <c r="AV46" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="51" spans="47:47">
-      <c r="AU51" t="s">
+    <row r="47" spans="48:48">
+      <c r="AV47" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="52" spans="47:47">
-      <c r="AU52" t="s">
+    <row r="48" spans="48:48">
+      <c r="AV48" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="53" spans="47:47">
-      <c r="AU53" t="s">
+    <row r="49" spans="48:48">
+      <c r="AV49" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="54" spans="47:47">
-      <c r="AU54" t="s">
+    <row r="50" spans="48:48">
+      <c r="AV50" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="55" spans="47:47">
-      <c r="AU55" t="s">
+    <row r="51" spans="48:48">
+      <c r="AV51" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="56" spans="47:47">
-      <c r="AU56" t="s">
+    <row r="52" spans="48:48">
+      <c r="AV52" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="57" spans="47:47">
-      <c r="AU57" t="s">
+    <row r="53" spans="48:48">
+      <c r="AV53" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="58" spans="47:47">
-      <c r="AU58" t="s">
+    <row r="54" spans="48:48">
+      <c r="AV54" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="59" spans="47:47">
-      <c r="AU59" t="s">
+    <row r="55" spans="48:48">
+      <c r="AV55" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="60" spans="47:47">
-      <c r="AU60" t="s">
+    <row r="56" spans="48:48">
+      <c r="AV56" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="61" spans="47:47">
-      <c r="AU61" t="s">
+    <row r="57" spans="48:48">
+      <c r="AV57" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="62" spans="47:47">
-      <c r="AU62" t="s">
+    <row r="58" spans="48:48">
+      <c r="AV58" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="63" spans="47:47">
-      <c r="AU63" t="s">
+    <row r="59" spans="48:48">
+      <c r="AV59" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="64" spans="47:47">
-      <c r="AU64" t="s">
+    <row r="60" spans="48:48">
+      <c r="AV60" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="65" spans="47:47">
-      <c r="AU65" t="s">
+    <row r="61" spans="48:48">
+      <c r="AV61" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="66" spans="47:47">
-      <c r="AU66" t="s">
+    <row r="62" spans="48:48">
+      <c r="AV62" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="67" spans="47:47">
-      <c r="AU67" t="s">
+    <row r="63" spans="48:48">
+      <c r="AV63" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="68" spans="47:47">
-      <c r="AU68" t="s">
+    <row r="64" spans="48:48">
+      <c r="AV64" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="69" spans="47:47">
-      <c r="AU69" t="s">
+    <row r="65" spans="48:48">
+      <c r="AV65" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="70" spans="47:47">
-      <c r="AU70" t="s">
+    <row r="66" spans="48:48">
+      <c r="AV66" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="71" spans="47:47">
-      <c r="AU71" t="s">
+    <row r="67" spans="48:48">
+      <c r="AV67" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="72" spans="47:47">
-      <c r="AU72" t="s">
+    <row r="68" spans="48:48">
+      <c r="AV68" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="73" spans="47:47">
-      <c r="AU73" t="s">
+    <row r="69" spans="48:48">
+      <c r="AV69" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="74" spans="47:47">
-      <c r="AU74" t="s">
+    <row r="70" spans="48:48">
+      <c r="AV70" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="75" spans="47:47">
-      <c r="AU75" t="s">
+    <row r="71" spans="48:48">
+      <c r="AV71" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="76" spans="47:47">
-      <c r="AU76" t="s">
+    <row r="72" spans="48:48">
+      <c r="AV72" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="77" spans="47:47">
-      <c r="AU77" t="s">
+    <row r="73" spans="48:48">
+      <c r="AV73" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="78" spans="47:47">
-      <c r="AU78" t="s">
+    <row r="74" spans="48:48">
+      <c r="AV74" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="79" spans="47:47">
-      <c r="AU79" t="s">
+    <row r="75" spans="48:48">
+      <c r="AV75" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="80" spans="47:47">
-      <c r="AU80" t="s">
+    <row r="76" spans="48:48">
+      <c r="AV76" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="81" spans="47:47">
-      <c r="AU81" t="s">
+    <row r="77" spans="48:48">
+      <c r="AV77" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="82" spans="47:47">
-      <c r="AU82" t="s">
+    <row r="78" spans="48:48">
+      <c r="AV78" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="83" spans="47:47">
-      <c r="AU83" t="s">
+    <row r="79" spans="48:48">
+      <c r="AV79" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="84" spans="47:47">
-      <c r="AU84" t="s">
+    <row r="80" spans="48:48">
+      <c r="AV80" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="85" spans="47:47">
-      <c r="AU85" t="s">
+    <row r="81" spans="48:48">
+      <c r="AV81" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="86" spans="47:47">
-      <c r="AU86" t="s">
+    <row r="82" spans="48:48">
+      <c r="AV82" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="87" spans="47:47">
-      <c r="AU87" t="s">
+    <row r="83" spans="48:48">
+      <c r="AV83" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="88" spans="47:47">
-      <c r="AU88" t="s">
+    <row r="84" spans="48:48">
+      <c r="AV84" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="89" spans="47:47">
-      <c r="AU89" t="s">
+    <row r="85" spans="48:48">
+      <c r="AV85" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="90" spans="47:47">
-      <c r="AU90" t="s">
+    <row r="86" spans="48:48">
+      <c r="AV86" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="91" spans="47:47">
-      <c r="AU91" t="s">
+    <row r="87" spans="48:48">
+      <c r="AV87" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="92" spans="47:47">
-      <c r="AU92" t="s">
+    <row r="88" spans="48:48">
+      <c r="AV88" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="93" spans="47:47">
-      <c r="AU93" t="s">
+    <row r="89" spans="48:48">
+      <c r="AV89" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="94" spans="47:47">
-      <c r="AU94" t="s">
+    <row r="90" spans="48:48">
+      <c r="AV90" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="95" spans="47:47">
-      <c r="AU95" t="s">
+    <row r="91" spans="48:48">
+      <c r="AV91" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="96" spans="47:47">
-      <c r="AU96" t="s">
+    <row r="92" spans="48:48">
+      <c r="AV92" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="97" spans="47:47">
-      <c r="AU97" t="s">
+    <row r="93" spans="48:48">
+      <c r="AV93" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="98" spans="47:47">
-      <c r="AU98" t="s">
+    <row r="94" spans="48:48">
+      <c r="AV94" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="99" spans="47:47">
-      <c r="AU99" t="s">
+    <row r="95" spans="48:48">
+      <c r="AV95" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="100" spans="47:47">
-      <c r="AU100" t="s">
+    <row r="96" spans="48:48">
+      <c r="AV96" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="101" spans="47:47">
-      <c r="AU101" t="s">
+    <row r="97" spans="48:48">
+      <c r="AV97" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="102" spans="47:47">
-      <c r="AU102" t="s">
+    <row r="98" spans="48:48">
+      <c r="AV98" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="103" spans="47:47">
-      <c r="AU103" t="s">
+    <row r="99" spans="48:48">
+      <c r="AV99" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="104" spans="47:47">
-      <c r="AU104" t="s">
+    <row r="100" spans="48:48">
+      <c r="AV100" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="47:47">
-      <c r="AU105" t="s">
+    <row r="101" spans="48:48">
+      <c r="AV101" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="47:47">
-      <c r="AU106" t="s">
+    <row r="102" spans="48:48">
+      <c r="AV102" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="107" spans="47:47">
-      <c r="AU107" t="s">
+    <row r="103" spans="48:48">
+      <c r="AV103" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="108" spans="47:47">
-      <c r="AU108" t="s">
+    <row r="104" spans="48:48">
+      <c r="AV104" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="109" spans="47:47">
-      <c r="AU109" t="s">
+    <row r="105" spans="48:48">
+      <c r="AV105" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="110" spans="47:47">
-      <c r="AU110" t="s">
+    <row r="106" spans="48:48">
+      <c r="AV106" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="111" spans="47:47">
-      <c r="AU111" t="s">
+    <row r="107" spans="48:48">
+      <c r="AV107" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="112" spans="47:47">
-      <c r="AU112" t="s">
+    <row r="108" spans="48:48">
+      <c r="AV108" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="113" spans="47:47">
-      <c r="AU113" t="s">
+    <row r="109" spans="48:48">
+      <c r="AV109" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="114" spans="47:47">
-      <c r="AU114" t="s">
+    <row r="110" spans="48:48">
+      <c r="AV110" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="115" spans="47:47">
-      <c r="AU115" t="s">
+    <row r="111" spans="48:48">
+      <c r="AV111" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="116" spans="47:47">
-      <c r="AU116" t="s">
+    <row r="112" spans="48:48">
+      <c r="AV112" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="117" spans="47:47">
-      <c r="AU117" t="s">
+    <row r="113" spans="48:48">
+      <c r="AV113" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="118" spans="47:47">
-      <c r="AU118" t="s">
+    <row r="114" spans="48:48">
+      <c r="AV114" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="119" spans="47:47">
-      <c r="AU119" t="s">
+    <row r="115" spans="48:48">
+      <c r="AV115" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="120" spans="47:47">
-      <c r="AU120" t="s">
+    <row r="116" spans="48:48">
+      <c r="AV116" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="121" spans="47:47">
-      <c r="AU121" t="s">
+    <row r="117" spans="48:48">
+      <c r="AV117" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="122" spans="47:47">
-      <c r="AU122" t="s">
+    <row r="118" spans="48:48">
+      <c r="AV118" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="123" spans="47:47">
-      <c r="AU123" t="s">
+    <row r="119" spans="48:48">
+      <c r="AV119" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="124" spans="47:47">
-      <c r="AU124" t="s">
+    <row r="120" spans="48:48">
+      <c r="AV120" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="125" spans="47:47">
-      <c r="AU125" t="s">
+    <row r="121" spans="48:48">
+      <c r="AV121" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="126" spans="47:47">
-      <c r="AU126" t="s">
+    <row r="122" spans="48:48">
+      <c r="AV122" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="127" spans="47:47">
-      <c r="AU127" t="s">
+    <row r="123" spans="48:48">
+      <c r="AV123" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="128" spans="47:47">
-      <c r="AU128" t="s">
+    <row r="124" spans="48:48">
+      <c r="AV124" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="129" spans="47:47">
-      <c r="AU129" t="s">
+    <row r="125" spans="48:48">
+      <c r="AV125" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="130" spans="47:47">
-      <c r="AU130" t="s">
+    <row r="126" spans="48:48">
+      <c r="AV126" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="131" spans="47:47">
-      <c r="AU131" t="s">
+    <row r="127" spans="48:48">
+      <c r="AV127" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="132" spans="47:47">
-      <c r="AU132" t="s">
+    <row r="128" spans="48:48">
+      <c r="AV128" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="133" spans="47:47">
-      <c r="AU133" t="s">
+    <row r="129" spans="48:48">
+      <c r="AV129" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="134" spans="47:47">
-      <c r="AU134" t="s">
+    <row r="130" spans="48:48">
+      <c r="AV130" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="135" spans="47:47">
-      <c r="AU135" t="s">
+    <row r="131" spans="48:48">
+      <c r="AV131" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="136" spans="47:47">
-      <c r="AU136" t="s">
+    <row r="132" spans="48:48">
+      <c r="AV132" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="137" spans="47:47">
-      <c r="AU137" t="s">
+    <row r="133" spans="48:48">
+      <c r="AV133" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="138" spans="47:47">
-      <c r="AU138" t="s">
+    <row r="134" spans="48:48">
+      <c r="AV134" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="139" spans="47:47">
-      <c r="AU139" t="s">
+    <row r="135" spans="48:48">
+      <c r="AV135" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="140" spans="47:47">
-      <c r="AU140" t="s">
+    <row r="136" spans="48:48">
+      <c r="AV136" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="141" spans="47:47">
-      <c r="AU141" t="s">
+    <row r="137" spans="48:48">
+      <c r="AV137" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="142" spans="47:47">
-      <c r="AU142" t="s">
+    <row r="138" spans="48:48">
+      <c r="AV138" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="143" spans="47:47">
-      <c r="AU143" t="s">
+    <row r="139" spans="48:48">
+      <c r="AV139" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="144" spans="47:47">
-      <c r="AU144" t="s">
+    <row r="140" spans="48:48">
+      <c r="AV140" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="145" spans="47:47">
-      <c r="AU145" t="s">
+    <row r="141" spans="48:48">
+      <c r="AV141" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="146" spans="47:47">
-      <c r="AU146" t="s">
+    <row r="142" spans="48:48">
+      <c r="AV142" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="147" spans="47:47">
-      <c r="AU147" t="s">
+    <row r="143" spans="48:48">
+      <c r="AV143" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="148" spans="47:47">
-      <c r="AU148" t="s">
+    <row r="144" spans="48:48">
+      <c r="AV144" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="149" spans="47:47">
-      <c r="AU149" t="s">
+    <row r="145" spans="48:48">
+      <c r="AV145" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="150" spans="47:47">
-      <c r="AU150" t="s">
+    <row r="146" spans="48:48">
+      <c r="AV146" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="151" spans="47:47">
-      <c r="AU151" t="s">
+    <row r="147" spans="48:48">
+      <c r="AV147" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="152" spans="47:47">
-      <c r="AU152" t="s">
+    <row r="148" spans="48:48">
+      <c r="AV148" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="153" spans="47:47">
-      <c r="AU153" t="s">
+    <row r="149" spans="48:48">
+      <c r="AV149" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="154" spans="47:47">
-      <c r="AU154" t="s">
+    <row r="150" spans="48:48">
+      <c r="AV150" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="155" spans="47:47">
-      <c r="AU155" t="s">
+    <row r="151" spans="48:48">
+      <c r="AV151" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="156" spans="47:47">
-      <c r="AU156" t="s">
+    <row r="152" spans="48:48">
+      <c r="AV152" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="157" spans="47:47">
-      <c r="AU157" t="s">
+    <row r="153" spans="48:48">
+      <c r="AV153" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="158" spans="47:47">
-      <c r="AU158" t="s">
+    <row r="154" spans="48:48">
+      <c r="AV154" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="159" spans="47:47">
-      <c r="AU159" t="s">
+    <row r="155" spans="48:48">
+      <c r="AV155" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="160" spans="47:47">
-      <c r="AU160" t="s">
+    <row r="156" spans="48:48">
+      <c r="AV156" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="161" spans="47:47">
-      <c r="AU161" t="s">
+    <row r="157" spans="48:48">
+      <c r="AV157" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="162" spans="47:47">
-      <c r="AU162" t="s">
+    <row r="158" spans="48:48">
+      <c r="AV158" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="163" spans="47:47">
-      <c r="AU163" t="s">
+    <row r="159" spans="48:48">
+      <c r="AV159" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="164" spans="47:47">
-      <c r="AU164" t="s">
+    <row r="160" spans="48:48">
+      <c r="AV160" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="165" spans="47:47">
-      <c r="AU165" t="s">
+    <row r="161" spans="48:48">
+      <c r="AV161" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="166" spans="47:47">
-      <c r="AU166" t="s">
+    <row r="162" spans="48:48">
+      <c r="AV162" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="167" spans="47:47">
-      <c r="AU167" t="s">
+    <row r="163" spans="48:48">
+      <c r="AV163" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="168" spans="47:47">
-      <c r="AU168" t="s">
+    <row r="164" spans="48:48">
+      <c r="AV164" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="169" spans="47:47">
-      <c r="AU169" t="s">
+    <row r="165" spans="48:48">
+      <c r="AV165" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="170" spans="47:47">
-      <c r="AU170" t="s">
+    <row r="166" spans="48:48">
+      <c r="AV166" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="171" spans="47:47">
-      <c r="AU171" t="s">
+    <row r="167" spans="48:48">
+      <c r="AV167" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="172" spans="47:47">
-      <c r="AU172" t="s">
+    <row r="168" spans="48:48">
+      <c r="AV168" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="173" spans="47:47">
-      <c r="AU173" t="s">
+    <row r="169" spans="48:48">
+      <c r="AV169" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="174" spans="47:47">
-      <c r="AU174" t="s">
+    <row r="170" spans="48:48">
+      <c r="AV170" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="175" spans="47:47">
-      <c r="AU175" t="s">
+    <row r="171" spans="48:48">
+      <c r="AV171" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="176" spans="47:47">
-      <c r="AU176" t="s">
+    <row r="172" spans="48:48">
+      <c r="AV172" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="177" spans="47:47">
-      <c r="AU177" t="s">
+    <row r="173" spans="48:48">
+      <c r="AV173" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="178" spans="47:47">
-      <c r="AU178" t="s">
+    <row r="174" spans="48:48">
+      <c r="AV174" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="179" spans="47:47">
-      <c r="AU179" t="s">
+    <row r="175" spans="48:48">
+      <c r="AV175" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="180" spans="47:47">
-      <c r="AU180" t="s">
+    <row r="176" spans="48:48">
+      <c r="AV176" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="181" spans="47:47">
-      <c r="AU181" t="s">
+    <row r="177" spans="48:48">
+      <c r="AV177" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="182" spans="47:47">
-      <c r="AU182" t="s">
+    <row r="178" spans="48:48">
+      <c r="AV178" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="183" spans="47:47">
-      <c r="AU183" t="s">
+    <row r="179" spans="48:48">
+      <c r="AV179" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="184" spans="47:47">
-      <c r="AU184" t="s">
+    <row r="180" spans="48:48">
+      <c r="AV180" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="185" spans="47:47">
-      <c r="AU185" t="s">
+    <row r="181" spans="48:48">
+      <c r="AV181" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="186" spans="47:47">
-      <c r="AU186" t="s">
+    <row r="182" spans="48:48">
+      <c r="AV182" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="187" spans="47:47">
-      <c r="AU187" t="s">
+    <row r="183" spans="48:48">
+      <c r="AV183" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="188" spans="47:47">
-      <c r="AU188" t="s">
+    <row r="184" spans="48:48">
+      <c r="AV184" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="189" spans="47:47">
-      <c r="AU189" t="s">
+    <row r="185" spans="48:48">
+      <c r="AV185" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="190" spans="47:47">
-      <c r="AU190" t="s">
+    <row r="186" spans="48:48">
+      <c r="AV186" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="191" spans="47:47">
-      <c r="AU191" t="s">
+    <row r="187" spans="48:48">
+      <c r="AV187" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="192" spans="47:47">
-      <c r="AU192" t="s">
+    <row r="188" spans="48:48">
+      <c r="AV188" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="193" spans="47:47">
-      <c r="AU193" t="s">
+    <row r="189" spans="48:48">
+      <c r="AV189" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="194" spans="47:47">
-      <c r="AU194" t="s">
+    <row r="190" spans="48:48">
+      <c r="AV190" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="195" spans="47:47">
-      <c r="AU195" t="s">
+    <row r="191" spans="48:48">
+      <c r="AV191" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="196" spans="47:47">
-      <c r="AU196" t="s">
+    <row r="192" spans="48:48">
+      <c r="AV192" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="197" spans="47:47">
-      <c r="AU197" t="s">
+    <row r="193" spans="48:48">
+      <c r="AV193" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="198" spans="47:47">
-      <c r="AU198" t="s">
+    <row r="194" spans="48:48">
+      <c r="AV194" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="199" spans="47:47">
-      <c r="AU199" t="s">
+    <row r="195" spans="48:48">
+      <c r="AV195" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="200" spans="47:47">
-      <c r="AU200" t="s">
+    <row r="196" spans="48:48">
+      <c r="AV196" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="201" spans="47:47">
-      <c r="AU201" t="s">
+    <row r="197" spans="48:48">
+      <c r="AV197" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="202" spans="47:47">
-      <c r="AU202" t="s">
+    <row r="198" spans="48:48">
+      <c r="AV198" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="203" spans="47:47">
-      <c r="AU203" t="s">
+    <row r="199" spans="48:48">
+      <c r="AV199" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="204" spans="47:47">
-      <c r="AU204" t="s">
+    <row r="200" spans="48:48">
+      <c r="AV200" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="205" spans="47:47">
-      <c r="AU205" t="s">
+    <row r="201" spans="48:48">
+      <c r="AV201" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="206" spans="47:47">
-      <c r="AU206" t="s">
+    <row r="202" spans="48:48">
+      <c r="AV202" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="207" spans="47:47">
-      <c r="AU207" t="s">
+    <row r="203" spans="48:48">
+      <c r="AV203" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="208" spans="47:47">
-      <c r="AU208" t="s">
+    <row r="204" spans="48:48">
+      <c r="AV204" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="209" spans="47:47">
-      <c r="AU209" t="s">
+    <row r="205" spans="48:48">
+      <c r="AV205" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="210" spans="47:47">
-      <c r="AU210" t="s">
+    <row r="206" spans="48:48">
+      <c r="AV206" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="211" spans="47:47">
-      <c r="AU211" t="s">
+    <row r="207" spans="48:48">
+      <c r="AV207" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="212" spans="47:47">
-      <c r="AU212" t="s">
+    <row r="208" spans="48:48">
+      <c r="AV208" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="213" spans="47:47">
-      <c r="AU213" t="s">
+    <row r="209" spans="48:48">
+      <c r="AV209" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="214" spans="47:47">
-      <c r="AU214" t="s">
+    <row r="210" spans="48:48">
+      <c r="AV210" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="215" spans="47:47">
-      <c r="AU215" t="s">
+    <row r="211" spans="48:48">
+      <c r="AV211" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="216" spans="47:47">
-      <c r="AU216" t="s">
+    <row r="212" spans="48:48">
+      <c r="AV212" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="217" spans="47:47">
-      <c r="AU217" t="s">
+    <row r="213" spans="48:48">
+      <c r="AV213" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="218" spans="47:47">
-      <c r="AU218" t="s">
+    <row r="214" spans="48:48">
+      <c r="AV214" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="219" spans="47:47">
-      <c r="AU219" t="s">
+    <row r="215" spans="48:48">
+      <c r="AV215" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="220" spans="47:47">
-      <c r="AU220" t="s">
+    <row r="216" spans="48:48">
+      <c r="AV216" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="221" spans="47:47">
-      <c r="AU221" t="s">
+    <row r="217" spans="48:48">
+      <c r="AV217" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="222" spans="47:47">
-      <c r="AU222" t="s">
+    <row r="218" spans="48:48">
+      <c r="AV218" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="223" spans="47:47">
-      <c r="AU223" t="s">
+    <row r="219" spans="48:48">
+      <c r="AV219" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="224" spans="47:47">
-      <c r="AU224" t="s">
+    <row r="220" spans="48:48">
+      <c r="AV220" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="225" spans="47:47">
-      <c r="AU225" t="s">
+    <row r="221" spans="48:48">
+      <c r="AV221" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="226" spans="47:47">
-      <c r="AU226" t="s">
+    <row r="222" spans="48:48">
+      <c r="AV222" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="227" spans="47:47">
-      <c r="AU227" t="s">
+    <row r="223" spans="48:48">
+      <c r="AV223" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="228" spans="47:47">
-      <c r="AU228" t="s">
+    <row r="224" spans="48:48">
+      <c r="AV224" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="229" spans="47:47">
-      <c r="AU229" t="s">
+    <row r="225" spans="48:48">
+      <c r="AV225" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="230" spans="47:47">
-      <c r="AU230" t="s">
+    <row r="226" spans="48:48">
+      <c r="AV226" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="231" spans="47:47">
-      <c r="AU231" t="s">
+    <row r="227" spans="48:48">
+      <c r="AV227" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="232" spans="47:47">
-      <c r="AU232" t="s">
+    <row r="228" spans="48:48">
+      <c r="AV228" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="233" spans="47:47">
-      <c r="AU233" t="s">
+    <row r="229" spans="48:48">
+      <c r="AV229" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="234" spans="47:47">
-      <c r="AU234" t="s">
+    <row r="230" spans="48:48">
+      <c r="AV230" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="235" spans="47:47">
-      <c r="AU235" t="s">
+    <row r="231" spans="48:48">
+      <c r="AV231" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="236" spans="47:47">
-      <c r="AU236" t="s">
+    <row r="232" spans="48:48">
+      <c r="AV232" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="237" spans="47:47">
-      <c r="AU237" t="s">
+    <row r="233" spans="48:48">
+      <c r="AV233" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="238" spans="47:47">
-      <c r="AU238" t="s">
+    <row r="234" spans="48:48">
+      <c r="AV234" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="239" spans="47:47">
-      <c r="AU239" t="s">
+    <row r="235" spans="48:48">
+      <c r="AV235" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="240" spans="47:47">
-      <c r="AU240" t="s">
+    <row r="236" spans="48:48">
+      <c r="AV236" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="241" spans="47:47">
-      <c r="AU241" t="s">
+    <row r="237" spans="48:48">
+      <c r="AV237" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="242" spans="47:47">
-      <c r="AU242" t="s">
+    <row r="238" spans="48:48">
+      <c r="AV238" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="243" spans="47:47">
-      <c r="AU243" t="s">
+    <row r="239" spans="48:48">
+      <c r="AV239" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="244" spans="47:47">
-      <c r="AU244" t="s">
+    <row r="240" spans="48:48">
+      <c r="AV240" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="245" spans="47:47">
-      <c r="AU245" t="s">
+    <row r="241" spans="48:48">
+      <c r="AV241" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="246" spans="47:47">
-      <c r="AU246" t="s">
+    <row r="242" spans="48:48">
+      <c r="AV242" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="247" spans="47:47">
-      <c r="AU247" t="s">
+    <row r="243" spans="48:48">
+      <c r="AV243" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="248" spans="47:47">
-      <c r="AU248" t="s">
+    <row r="244" spans="48:48">
+      <c r="AV244" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="249" spans="47:47">
-      <c r="AU249" t="s">
+    <row r="245" spans="48:48">
+      <c r="AV245" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="250" spans="47:47">
-      <c r="AU250" t="s">
+    <row r="246" spans="48:48">
+      <c r="AV246" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="251" spans="47:47">
-      <c r="AU251" t="s">
+    <row r="247" spans="48:48">
+      <c r="AV247" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="252" spans="47:47">
-      <c r="AU252" t="s">
+    <row r="248" spans="48:48">
+      <c r="AV248" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="253" spans="47:47">
-      <c r="AU253" t="s">
+    <row r="249" spans="48:48">
+      <c r="AV249" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="254" spans="47:47">
-      <c r="AU254" t="s">
+    <row r="250" spans="48:48">
+      <c r="AV250" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="255" spans="47:47">
-      <c r="AU255" t="s">
+    <row r="251" spans="48:48">
+      <c r="AV251" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="256" spans="47:47">
-      <c r="AU256" t="s">
+    <row r="252" spans="48:48">
+      <c r="AV252" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="257" spans="47:47">
-      <c r="AU257" t="s">
+    <row r="253" spans="48:48">
+      <c r="AV253" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="258" spans="47:47">
-      <c r="AU258" t="s">
+    <row r="254" spans="48:48">
+      <c r="AV254" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="259" spans="47:47">
-      <c r="AU259" t="s">
+    <row r="255" spans="48:48">
+      <c r="AV255" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="260" spans="47:47">
-      <c r="AU260" t="s">
+    <row r="256" spans="48:48">
+      <c r="AV256" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="261" spans="47:47">
-      <c r="AU261" t="s">
+    <row r="257" spans="48:48">
+      <c r="AV257" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="262" spans="47:47">
-      <c r="AU262" t="s">
+    <row r="258" spans="48:48">
+      <c r="AV258" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="263" spans="47:47">
-      <c r="AU263" t="s">
+    <row r="259" spans="48:48">
+      <c r="AV259" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="264" spans="47:47">
-      <c r="AU264" t="s">
+    <row r="260" spans="48:48">
+      <c r="AV260" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="265" spans="47:47">
-      <c r="AU265" t="s">
+    <row r="261" spans="48:48">
+      <c r="AV261" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="266" spans="47:47">
-      <c r="AU266" t="s">
+    <row r="262" spans="48:48">
+      <c r="AV262" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="267" spans="47:47">
-      <c r="AU267" t="s">
+    <row r="263" spans="48:48">
+      <c r="AV263" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="268" spans="47:47">
-      <c r="AU268" t="s">
+    <row r="264" spans="48:48">
+      <c r="AV264" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="269" spans="47:47">
-      <c r="AU269" t="s">
+    <row r="265" spans="48:48">
+      <c r="AV265" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="270" spans="47:47">
-      <c r="AU270" t="s">
+    <row r="266" spans="48:48">
+      <c r="AV266" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="271" spans="47:47">
-      <c r="AU271" t="s">
+    <row r="267" spans="48:48">
+      <c r="AV267" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="272" spans="47:47">
-      <c r="AU272" t="s">
+    <row r="268" spans="48:48">
+      <c r="AV268" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="273" spans="47:47">
-      <c r="AU273" t="s">
+    <row r="269" spans="48:48">
+      <c r="AV269" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="274" spans="47:47">
-      <c r="AU274" t="s">
+    <row r="270" spans="48:48">
+      <c r="AV270" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="275" spans="47:47">
-      <c r="AU275" t="s">
+    <row r="271" spans="48:48">
+      <c r="AV271" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="276" spans="47:47">
-      <c r="AU276" t="s">
+    <row r="272" spans="48:48">
+      <c r="AV272" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="277" spans="47:47">
-      <c r="AU277" t="s">
+    <row r="273" spans="48:48">
+      <c r="AV273" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="278" spans="47:47">
-      <c r="AU278" t="s">
+    <row r="274" spans="48:48">
+      <c r="AV274" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="279" spans="47:47">
-      <c r="AU279" t="s">
+    <row r="275" spans="48:48">
+      <c r="AV275" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="280" spans="47:47">
-      <c r="AU280" t="s">
+    <row r="276" spans="48:48">
+      <c r="AV276" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="281" spans="47:47">
-      <c r="AU281" t="s">
+    <row r="277" spans="48:48">
+      <c r="AV277" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="282" spans="47:47">
-      <c r="AU282" t="s">
+    <row r="278" spans="48:48">
+      <c r="AV278" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="283" spans="47:47">
-      <c r="AU283" t="s">
+    <row r="279" spans="48:48">
+      <c r="AV279" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="284" spans="47:47">
-      <c r="AU284" t="s">
+    <row r="280" spans="48:48">
+      <c r="AV280" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="285" spans="47:47">
-      <c r="AU285" t="s">
+    <row r="281" spans="48:48">
+      <c r="AV281" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="286" spans="47:47">
-      <c r="AU286" t="s">
+    <row r="282" spans="48:48">
+      <c r="AV282" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="287" spans="47:47">
-      <c r="AU287" t="s">
+    <row r="283" spans="48:48">
+      <c r="AV283" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="288" spans="47:47">
-      <c r="AU288" t="s">
+    <row r="284" spans="48:48">
+      <c r="AV284" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="289" spans="47:47">
-      <c r="AU289" t="s">
+    <row r="285" spans="48:48">
+      <c r="AV285" t="s">
         <v>690</v>
+      </c>
+    </row>
+    <row r="286" spans="48:48">
+      <c r="AV286" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="287" spans="48:48">
+      <c r="AV287" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="288" spans="48:48">
+      <c r="AV288" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="289" spans="48:48">
+      <c r="AV289" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="290" spans="48:48">
+      <c r="AV290" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="291" spans="48:48">
+      <c r="AV291" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="292" spans="48:48">
+      <c r="AV292" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="293" spans="48:48">
+      <c r="AV293" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="294" spans="48:48">
+      <c r="AV294" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000027/metadata_template_ERC000027.xlsx
+++ b/templates/ERC000027/metadata_template_ERC000027.xlsx
@@ -17,28 +17,28 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="environmentalpackage">'cv_sample'!$AH$1:$AH$1</definedName>
+    <definedName name="environmentalpackage">'cv_sample'!$AI$1:$AI$1</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AV$1:$AV$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$L$1:$L$5</definedName>
-    <definedName name="oxygenationstatusofsample">'cv_sample'!$S$1:$S$2</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$M$1:$M$5</definedName>
+    <definedName name="oxygenationstatusofsample">'cv_sample'!$T$1:$T$2</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$N$1:$N$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$AD$1:$AD$3</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$O$1:$O$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$AE$1:$AE$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="tidalstage">'cv_sample'!$BI$1:$BI$2</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$K$1:$K$30</definedName>
+    <definedName name="tidalstage">'cv_sample'!$BJ$1:$BJ$2</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$L$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="888">
   <si>
     <t>alias</t>
   </si>
@@ -854,6 +854,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -4219,13 +4225,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EI2"/>
+  <dimension ref="A1:EJ2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139">
+    <row r="1" spans="1:140">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4257,16 +4263,16 @@
         <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>323</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>334</v>
@@ -4281,7 +4287,7 @@
         <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>346</v>
@@ -4314,7 +4320,7 @@
         <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>371</v>
@@ -4326,7 +4332,7 @@
         <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
         <v>380</v>
@@ -4368,7 +4374,7 @@
         <v>404</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>700</v>
+        <v>406</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>702</v>
@@ -4407,7 +4413,7 @@
         <v>724</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>730</v>
@@ -4643,8 +4649,11 @@
       <c r="EI1" s="1" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="2" spans="1:139" ht="150" customHeight="1">
+      <c r="EJ1" s="1" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="2" spans="1:140" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4676,16 +4685,16 @@
         <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>324</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>335</v>
@@ -4700,7 +4709,7 @@
         <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>347</v>
@@ -4733,7 +4742,7 @@
         <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>372</v>
@@ -4745,7 +4754,7 @@
         <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
         <v>381</v>
@@ -4787,7 +4796,7 @@
         <v>405</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>701</v>
+        <v>407</v>
       </c>
       <c r="AW2" s="2" t="s">
         <v>703</v>
@@ -4826,7 +4835,7 @@
         <v>725</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="BJ2" s="2" t="s">
         <v>731</v>
@@ -5062,31 +5071,34 @@
       <c r="EI2" s="2" t="s">
         <v>885</v>
       </c>
+      <c r="EJ2" s="2" t="s">
+        <v>887</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
       <formula1>oxygenationstatusofsample</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3:AH101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI3:AI101">
       <formula1>environmentalpackage</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3:AV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ3:BJ101">
       <formula1>tidalstage</formula1>
     </dataValidation>
   </dataValidations>
@@ -5096,1627 +5108,1627 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="K1:BI294"/>
+  <dimension ref="L1:BJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="11:61">
-      <c r="K1" t="s">
-        <v>284</v>
-      </c>
+    <row r="1" spans="12:62">
       <c r="L1" t="s">
-        <v>316</v>
-      </c>
-      <c r="N1" t="s">
-        <v>325</v>
-      </c>
-      <c r="S1" t="s">
-        <v>342</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>366</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>377</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>406</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="2" spans="11:61">
-      <c r="K2" t="s">
-        <v>285</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="M1" t="s">
+        <v>318</v>
+      </c>
+      <c r="O1" t="s">
+        <v>327</v>
+      </c>
+      <c r="T1" t="s">
+        <v>344</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>368</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>379</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>408</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="2" spans="12:62">
       <c r="L2" t="s">
-        <v>317</v>
-      </c>
-      <c r="N2" t="s">
-        <v>326</v>
-      </c>
-      <c r="S2" t="s">
-        <v>343</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>367</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="3" spans="11:61">
-      <c r="K3" t="s">
-        <v>286</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="M2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O2" t="s">
+        <v>328</v>
+      </c>
+      <c r="T2" t="s">
+        <v>345</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>369</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>409</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="3" spans="12:62">
       <c r="L3" t="s">
-        <v>318</v>
-      </c>
-      <c r="N3" t="s">
-        <v>327</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>368</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="4" spans="11:61">
-      <c r="K4" t="s">
-        <v>287</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="M3" t="s">
+        <v>320</v>
+      </c>
+      <c r="O3" t="s">
+        <v>329</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>370</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="12:62">
       <c r="L4" t="s">
-        <v>319</v>
-      </c>
-      <c r="N4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="5" spans="11:61">
-      <c r="K5" t="s">
-        <v>288</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="M4" t="s">
+        <v>321</v>
+      </c>
+      <c r="O4" t="s">
+        <v>330</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="12:62">
       <c r="L5" t="s">
-        <v>320</v>
-      </c>
-      <c r="N5" t="s">
-        <v>329</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="6" spans="11:61">
-      <c r="K6" t="s">
-        <v>289</v>
-      </c>
-      <c r="N6" t="s">
-        <v>330</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" spans="11:61">
-      <c r="K7" t="s">
         <v>290</v>
       </c>
-      <c r="N7" t="s">
+      <c r="M5" t="s">
+        <v>322</v>
+      </c>
+      <c r="O5" t="s">
         <v>331</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="8" spans="11:61">
-      <c r="K8" t="s">
+    <row r="6" spans="12:62">
+      <c r="L6" t="s">
         <v>291</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="O6" t="s">
+        <v>332</v>
+      </c>
+      <c r="AW6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="9" spans="11:61">
-      <c r="K9" t="s">
+    <row r="7" spans="12:62">
+      <c r="L7" t="s">
         <v>292</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="O7" t="s">
+        <v>333</v>
+      </c>
+      <c r="AW7" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="10" spans="11:61">
-      <c r="K10" t="s">
+    <row r="8" spans="12:62">
+      <c r="L8" t="s">
         <v>293</v>
       </c>
-      <c r="AV10" t="s">
+      <c r="AW8" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="11" spans="11:61">
-      <c r="K11" t="s">
+    <row r="9" spans="12:62">
+      <c r="L9" t="s">
         <v>294</v>
       </c>
-      <c r="AV11" t="s">
+      <c r="AW9" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="12" spans="11:61">
-      <c r="K12" t="s">
+    <row r="10" spans="12:62">
+      <c r="L10" t="s">
         <v>295</v>
       </c>
-      <c r="AV12" t="s">
+      <c r="AW10" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="11:61">
-      <c r="K13" t="s">
+    <row r="11" spans="12:62">
+      <c r="L11" t="s">
         <v>296</v>
       </c>
-      <c r="AV13" t="s">
+      <c r="AW11" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="14" spans="11:61">
-      <c r="K14" t="s">
+    <row r="12" spans="12:62">
+      <c r="L12" t="s">
         <v>297</v>
       </c>
-      <c r="AV14" t="s">
+      <c r="AW12" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="15" spans="11:61">
-      <c r="K15" t="s">
+    <row r="13" spans="12:62">
+      <c r="L13" t="s">
         <v>298</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AW13" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="16" spans="11:61">
-      <c r="K16" t="s">
+    <row r="14" spans="12:62">
+      <c r="L14" t="s">
         <v>299</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AW14" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="17" spans="11:48">
-      <c r="K17" t="s">
+    <row r="15" spans="12:62">
+      <c r="L15" t="s">
         <v>300</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AW15" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="18" spans="11:48">
-      <c r="K18" t="s">
+    <row r="16" spans="12:62">
+      <c r="L16" t="s">
         <v>301</v>
       </c>
-      <c r="AV18" t="s">
+      <c r="AW16" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="19" spans="11:48">
-      <c r="K19" t="s">
+    <row r="17" spans="12:49">
+      <c r="L17" t="s">
         <v>302</v>
       </c>
-      <c r="AV19" t="s">
+      <c r="AW17" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="20" spans="11:48">
-      <c r="K20" t="s">
+    <row r="18" spans="12:49">
+      <c r="L18" t="s">
         <v>303</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AW18" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="11:48">
-      <c r="K21" t="s">
+    <row r="19" spans="12:49">
+      <c r="L19" t="s">
         <v>304</v>
       </c>
-      <c r="AV21" t="s">
+      <c r="AW19" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="22" spans="11:48">
-      <c r="K22" t="s">
+    <row r="20" spans="12:49">
+      <c r="L20" t="s">
         <v>305</v>
       </c>
-      <c r="AV22" t="s">
+      <c r="AW20" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="23" spans="11:48">
-      <c r="K23" t="s">
+    <row r="21" spans="12:49">
+      <c r="L21" t="s">
         <v>306</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AW21" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="24" spans="11:48">
-      <c r="K24" t="s">
+    <row r="22" spans="12:49">
+      <c r="L22" t="s">
         <v>307</v>
       </c>
-      <c r="AV24" t="s">
+      <c r="AW22" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="25" spans="11:48">
-      <c r="K25" t="s">
+    <row r="23" spans="12:49">
+      <c r="L23" t="s">
         <v>308</v>
       </c>
-      <c r="AV25" t="s">
+      <c r="AW23" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="26" spans="11:48">
-      <c r="K26" t="s">
+    <row r="24" spans="12:49">
+      <c r="L24" t="s">
         <v>309</v>
       </c>
-      <c r="AV26" t="s">
+      <c r="AW24" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="27" spans="11:48">
-      <c r="K27" t="s">
+    <row r="25" spans="12:49">
+      <c r="L25" t="s">
         <v>310</v>
       </c>
-      <c r="AV27" t="s">
+      <c r="AW25" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="11:48">
-      <c r="K28" t="s">
+    <row r="26" spans="12:49">
+      <c r="L26" t="s">
         <v>311</v>
       </c>
-      <c r="AV28" t="s">
+      <c r="AW26" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="29" spans="11:48">
-      <c r="K29" t="s">
+    <row r="27" spans="12:49">
+      <c r="L27" t="s">
         <v>312</v>
       </c>
-      <c r="AV29" t="s">
+      <c r="AW27" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="30" spans="11:48">
-      <c r="K30" t="s">
+    <row r="28" spans="12:49">
+      <c r="L28" t="s">
         <v>313</v>
       </c>
-      <c r="AV30" t="s">
+      <c r="AW28" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="31" spans="11:48">
-      <c r="AV31" t="s">
+    <row r="29" spans="12:49">
+      <c r="L29" t="s">
+        <v>314</v>
+      </c>
+      <c r="AW29" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="32" spans="11:48">
-      <c r="AV32" t="s">
+    <row r="30" spans="12:49">
+      <c r="L30" t="s">
+        <v>315</v>
+      </c>
+      <c r="AW30" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="33" spans="48:48">
-      <c r="AV33" t="s">
+    <row r="31" spans="12:49">
+      <c r="AW31" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="34" spans="48:48">
-      <c r="AV34" t="s">
+    <row r="32" spans="12:49">
+      <c r="AW32" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="35" spans="48:48">
-      <c r="AV35" t="s">
+    <row r="33" spans="49:49">
+      <c r="AW33" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="36" spans="48:48">
-      <c r="AV36" t="s">
+    <row r="34" spans="49:49">
+      <c r="AW34" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="48:48">
-      <c r="AV37" t="s">
+    <row r="35" spans="49:49">
+      <c r="AW35" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="38" spans="48:48">
-      <c r="AV38" t="s">
+    <row r="36" spans="49:49">
+      <c r="AW36" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="39" spans="48:48">
-      <c r="AV39" t="s">
+    <row r="37" spans="49:49">
+      <c r="AW37" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="40" spans="48:48">
-      <c r="AV40" t="s">
+    <row r="38" spans="49:49">
+      <c r="AW38" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="41" spans="48:48">
-      <c r="AV41" t="s">
+    <row r="39" spans="49:49">
+      <c r="AW39" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="42" spans="48:48">
-      <c r="AV42" t="s">
+    <row r="40" spans="49:49">
+      <c r="AW40" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="43" spans="48:48">
-      <c r="AV43" t="s">
+    <row r="41" spans="49:49">
+      <c r="AW41" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="44" spans="48:48">
-      <c r="AV44" t="s">
+    <row r="42" spans="49:49">
+      <c r="AW42" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="45" spans="48:48">
-      <c r="AV45" t="s">
+    <row r="43" spans="49:49">
+      <c r="AW43" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="48:48">
-      <c r="AV46" t="s">
+    <row r="44" spans="49:49">
+      <c r="AW44" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="47" spans="48:48">
-      <c r="AV47" t="s">
+    <row r="45" spans="49:49">
+      <c r="AW45" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="48" spans="48:48">
-      <c r="AV48" t="s">
+    <row r="46" spans="49:49">
+      <c r="AW46" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="49" spans="48:48">
-      <c r="AV49" t="s">
+    <row r="47" spans="49:49">
+      <c r="AW47" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="50" spans="48:48">
-      <c r="AV50" t="s">
+    <row r="48" spans="49:49">
+      <c r="AW48" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="51" spans="48:48">
-      <c r="AV51" t="s">
+    <row r="49" spans="49:49">
+      <c r="AW49" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="52" spans="48:48">
-      <c r="AV52" t="s">
+    <row r="50" spans="49:49">
+      <c r="AW50" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="53" spans="48:48">
-      <c r="AV53" t="s">
+    <row r="51" spans="49:49">
+      <c r="AW51" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="54" spans="48:48">
-      <c r="AV54" t="s">
+    <row r="52" spans="49:49">
+      <c r="AW52" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="55" spans="48:48">
-      <c r="AV55" t="s">
+    <row r="53" spans="49:49">
+      <c r="AW53" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="48:48">
-      <c r="AV56" t="s">
+    <row r="54" spans="49:49">
+      <c r="AW54" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="57" spans="48:48">
-      <c r="AV57" t="s">
+    <row r="55" spans="49:49">
+      <c r="AW55" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="58" spans="48:48">
-      <c r="AV58" t="s">
+    <row r="56" spans="49:49">
+      <c r="AW56" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="59" spans="48:48">
-      <c r="AV59" t="s">
+    <row r="57" spans="49:49">
+      <c r="AW57" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="60" spans="48:48">
-      <c r="AV60" t="s">
+    <row r="58" spans="49:49">
+      <c r="AW58" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="61" spans="48:48">
-      <c r="AV61" t="s">
+    <row r="59" spans="49:49">
+      <c r="AW59" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="62" spans="48:48">
-      <c r="AV62" t="s">
+    <row r="60" spans="49:49">
+      <c r="AW60" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="63" spans="48:48">
-      <c r="AV63" t="s">
+    <row r="61" spans="49:49">
+      <c r="AW61" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="64" spans="48:48">
-      <c r="AV64" t="s">
+    <row r="62" spans="49:49">
+      <c r="AW62" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="65" spans="48:48">
-      <c r="AV65" t="s">
+    <row r="63" spans="49:49">
+      <c r="AW63" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="66" spans="48:48">
-      <c r="AV66" t="s">
+    <row r="64" spans="49:49">
+      <c r="AW64" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="67" spans="48:48">
-      <c r="AV67" t="s">
+    <row r="65" spans="49:49">
+      <c r="AW65" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="68" spans="48:48">
-      <c r="AV68" t="s">
+    <row r="66" spans="49:49">
+      <c r="AW66" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="69" spans="48:48">
-      <c r="AV69" t="s">
+    <row r="67" spans="49:49">
+      <c r="AW67" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="70" spans="48:48">
-      <c r="AV70" t="s">
+    <row r="68" spans="49:49">
+      <c r="AW68" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="71" spans="48:48">
-      <c r="AV71" t="s">
+    <row r="69" spans="49:49">
+      <c r="AW69" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="72" spans="48:48">
-      <c r="AV72" t="s">
+    <row r="70" spans="49:49">
+      <c r="AW70" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="73" spans="48:48">
-      <c r="AV73" t="s">
+    <row r="71" spans="49:49">
+      <c r="AW71" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="74" spans="48:48">
-      <c r="AV74" t="s">
+    <row r="72" spans="49:49">
+      <c r="AW72" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="75" spans="48:48">
-      <c r="AV75" t="s">
+    <row r="73" spans="49:49">
+      <c r="AW73" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="76" spans="48:48">
-      <c r="AV76" t="s">
+    <row r="74" spans="49:49">
+      <c r="AW74" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="77" spans="48:48">
-      <c r="AV77" t="s">
+    <row r="75" spans="49:49">
+      <c r="AW75" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="78" spans="48:48">
-      <c r="AV78" t="s">
+    <row r="76" spans="49:49">
+      <c r="AW76" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="79" spans="48:48">
-      <c r="AV79" t="s">
+    <row r="77" spans="49:49">
+      <c r="AW77" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="80" spans="48:48">
-      <c r="AV80" t="s">
+    <row r="78" spans="49:49">
+      <c r="AW78" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="81" spans="48:48">
-      <c r="AV81" t="s">
+    <row r="79" spans="49:49">
+      <c r="AW79" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="82" spans="48:48">
-      <c r="AV82" t="s">
+    <row r="80" spans="49:49">
+      <c r="AW80" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="83" spans="48:48">
-      <c r="AV83" t="s">
+    <row r="81" spans="49:49">
+      <c r="AW81" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="84" spans="48:48">
-      <c r="AV84" t="s">
+    <row r="82" spans="49:49">
+      <c r="AW82" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="85" spans="48:48">
-      <c r="AV85" t="s">
+    <row r="83" spans="49:49">
+      <c r="AW83" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="86" spans="48:48">
-      <c r="AV86" t="s">
+    <row r="84" spans="49:49">
+      <c r="AW84" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="87" spans="48:48">
-      <c r="AV87" t="s">
+    <row r="85" spans="49:49">
+      <c r="AW85" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="88" spans="48:48">
-      <c r="AV88" t="s">
+    <row r="86" spans="49:49">
+      <c r="AW86" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="89" spans="48:48">
-      <c r="AV89" t="s">
+    <row r="87" spans="49:49">
+      <c r="AW87" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="90" spans="48:48">
-      <c r="AV90" t="s">
+    <row r="88" spans="49:49">
+      <c r="AW88" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="91" spans="48:48">
-      <c r="AV91" t="s">
+    <row r="89" spans="49:49">
+      <c r="AW89" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="92" spans="48:48">
-      <c r="AV92" t="s">
+    <row r="90" spans="49:49">
+      <c r="AW90" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="93" spans="48:48">
-      <c r="AV93" t="s">
+    <row r="91" spans="49:49">
+      <c r="AW91" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="94" spans="48:48">
-      <c r="AV94" t="s">
+    <row r="92" spans="49:49">
+      <c r="AW92" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="95" spans="48:48">
-      <c r="AV95" t="s">
+    <row r="93" spans="49:49">
+      <c r="AW93" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="96" spans="48:48">
-      <c r="AV96" t="s">
+    <row r="94" spans="49:49">
+      <c r="AW94" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="97" spans="48:48">
-      <c r="AV97" t="s">
+    <row r="95" spans="49:49">
+      <c r="AW95" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="98" spans="48:48">
-      <c r="AV98" t="s">
+    <row r="96" spans="49:49">
+      <c r="AW96" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="99" spans="48:48">
-      <c r="AV99" t="s">
+    <row r="97" spans="49:49">
+      <c r="AW97" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="100" spans="48:48">
-      <c r="AV100" t="s">
+    <row r="98" spans="49:49">
+      <c r="AW98" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="101" spans="48:48">
-      <c r="AV101" t="s">
+    <row r="99" spans="49:49">
+      <c r="AW99" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="102" spans="48:48">
-      <c r="AV102" t="s">
+    <row r="100" spans="49:49">
+      <c r="AW100" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="103" spans="48:48">
-      <c r="AV103" t="s">
+    <row r="101" spans="49:49">
+      <c r="AW101" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="104" spans="48:48">
-      <c r="AV104" t="s">
+    <row r="102" spans="49:49">
+      <c r="AW102" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="105" spans="48:48">
-      <c r="AV105" t="s">
+    <row r="103" spans="49:49">
+      <c r="AW103" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="106" spans="48:48">
-      <c r="AV106" t="s">
+    <row r="104" spans="49:49">
+      <c r="AW104" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="107" spans="48:48">
-      <c r="AV107" t="s">
+    <row r="105" spans="49:49">
+      <c r="AW105" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="108" spans="48:48">
-      <c r="AV108" t="s">
+    <row r="106" spans="49:49">
+      <c r="AW106" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="109" spans="48:48">
-      <c r="AV109" t="s">
+    <row r="107" spans="49:49">
+      <c r="AW107" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="110" spans="48:48">
-      <c r="AV110" t="s">
+    <row r="108" spans="49:49">
+      <c r="AW108" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="111" spans="48:48">
-      <c r="AV111" t="s">
+    <row r="109" spans="49:49">
+      <c r="AW109" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="112" spans="48:48">
-      <c r="AV112" t="s">
+    <row r="110" spans="49:49">
+      <c r="AW110" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="113" spans="48:48">
-      <c r="AV113" t="s">
+    <row r="111" spans="49:49">
+      <c r="AW111" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="114" spans="48:48">
-      <c r="AV114" t="s">
+    <row r="112" spans="49:49">
+      <c r="AW112" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="115" spans="48:48">
-      <c r="AV115" t="s">
+    <row r="113" spans="49:49">
+      <c r="AW113" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="116" spans="48:48">
-      <c r="AV116" t="s">
+    <row r="114" spans="49:49">
+      <c r="AW114" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="117" spans="48:48">
-      <c r="AV117" t="s">
+    <row r="115" spans="49:49">
+      <c r="AW115" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="118" spans="48:48">
-      <c r="AV118" t="s">
+    <row r="116" spans="49:49">
+      <c r="AW116" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="119" spans="48:48">
-      <c r="AV119" t="s">
+    <row r="117" spans="49:49">
+      <c r="AW117" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="120" spans="48:48">
-      <c r="AV120" t="s">
+    <row r="118" spans="49:49">
+      <c r="AW118" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="121" spans="48:48">
-      <c r="AV121" t="s">
+    <row r="119" spans="49:49">
+      <c r="AW119" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="122" spans="48:48">
-      <c r="AV122" t="s">
+    <row r="120" spans="49:49">
+      <c r="AW120" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="123" spans="48:48">
-      <c r="AV123" t="s">
+    <row r="121" spans="49:49">
+      <c r="AW121" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="124" spans="48:48">
-      <c r="AV124" t="s">
+    <row r="122" spans="49:49">
+      <c r="AW122" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="125" spans="48:48">
-      <c r="AV125" t="s">
+    <row r="123" spans="49:49">
+      <c r="AW123" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="126" spans="48:48">
-      <c r="AV126" t="s">
+    <row r="124" spans="49:49">
+      <c r="AW124" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="127" spans="48:48">
-      <c r="AV127" t="s">
+    <row r="125" spans="49:49">
+      <c r="AW125" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="128" spans="48:48">
-      <c r="AV128" t="s">
+    <row r="126" spans="49:49">
+      <c r="AW126" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="129" spans="48:48">
-      <c r="AV129" t="s">
+    <row r="127" spans="49:49">
+      <c r="AW127" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="130" spans="48:48">
-      <c r="AV130" t="s">
+    <row r="128" spans="49:49">
+      <c r="AW128" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="131" spans="48:48">
-      <c r="AV131" t="s">
+    <row r="129" spans="49:49">
+      <c r="AW129" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="132" spans="48:48">
-      <c r="AV132" t="s">
+    <row r="130" spans="49:49">
+      <c r="AW130" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="133" spans="48:48">
-      <c r="AV133" t="s">
+    <row r="131" spans="49:49">
+      <c r="AW131" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="134" spans="48:48">
-      <c r="AV134" t="s">
+    <row r="132" spans="49:49">
+      <c r="AW132" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="135" spans="48:48">
-      <c r="AV135" t="s">
+    <row r="133" spans="49:49">
+      <c r="AW133" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="136" spans="48:48">
-      <c r="AV136" t="s">
+    <row r="134" spans="49:49">
+      <c r="AW134" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="137" spans="48:48">
-      <c r="AV137" t="s">
+    <row r="135" spans="49:49">
+      <c r="AW135" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="138" spans="48:48">
-      <c r="AV138" t="s">
+    <row r="136" spans="49:49">
+      <c r="AW136" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="139" spans="48:48">
-      <c r="AV139" t="s">
+    <row r="137" spans="49:49">
+      <c r="AW137" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="140" spans="48:48">
-      <c r="AV140" t="s">
+    <row r="138" spans="49:49">
+      <c r="AW138" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="141" spans="48:48">
-      <c r="AV141" t="s">
+    <row r="139" spans="49:49">
+      <c r="AW139" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="142" spans="48:48">
-      <c r="AV142" t="s">
+    <row r="140" spans="49:49">
+      <c r="AW140" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="143" spans="48:48">
-      <c r="AV143" t="s">
+    <row r="141" spans="49:49">
+      <c r="AW141" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="144" spans="48:48">
-      <c r="AV144" t="s">
+    <row r="142" spans="49:49">
+      <c r="AW142" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="145" spans="48:48">
-      <c r="AV145" t="s">
+    <row r="143" spans="49:49">
+      <c r="AW143" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="146" spans="48:48">
-      <c r="AV146" t="s">
+    <row r="144" spans="49:49">
+      <c r="AW144" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="147" spans="48:48">
-      <c r="AV147" t="s">
+    <row r="145" spans="49:49">
+      <c r="AW145" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="148" spans="48:48">
-      <c r="AV148" t="s">
+    <row r="146" spans="49:49">
+      <c r="AW146" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="149" spans="48:48">
-      <c r="AV149" t="s">
+    <row r="147" spans="49:49">
+      <c r="AW147" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="150" spans="48:48">
-      <c r="AV150" t="s">
+    <row r="148" spans="49:49">
+      <c r="AW148" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="151" spans="48:48">
-      <c r="AV151" t="s">
+    <row r="149" spans="49:49">
+      <c r="AW149" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="152" spans="48:48">
-      <c r="AV152" t="s">
+    <row r="150" spans="49:49">
+      <c r="AW150" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="153" spans="48:48">
-      <c r="AV153" t="s">
+    <row r="151" spans="49:49">
+      <c r="AW151" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="154" spans="48:48">
-      <c r="AV154" t="s">
+    <row r="152" spans="49:49">
+      <c r="AW152" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="155" spans="48:48">
-      <c r="AV155" t="s">
+    <row r="153" spans="49:49">
+      <c r="AW153" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="156" spans="48:48">
-      <c r="AV156" t="s">
+    <row r="154" spans="49:49">
+      <c r="AW154" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="157" spans="48:48">
-      <c r="AV157" t="s">
+    <row r="155" spans="49:49">
+      <c r="AW155" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="158" spans="48:48">
-      <c r="AV158" t="s">
+    <row r="156" spans="49:49">
+      <c r="AW156" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="159" spans="48:48">
-      <c r="AV159" t="s">
+    <row r="157" spans="49:49">
+      <c r="AW157" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="160" spans="48:48">
-      <c r="AV160" t="s">
+    <row r="158" spans="49:49">
+      <c r="AW158" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="161" spans="48:48">
-      <c r="AV161" t="s">
+    <row r="159" spans="49:49">
+      <c r="AW159" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="162" spans="48:48">
-      <c r="AV162" t="s">
+    <row r="160" spans="49:49">
+      <c r="AW160" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="163" spans="48:48">
-      <c r="AV163" t="s">
+    <row r="161" spans="49:49">
+      <c r="AW161" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="164" spans="48:48">
-      <c r="AV164" t="s">
+    <row r="162" spans="49:49">
+      <c r="AW162" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="165" spans="48:48">
-      <c r="AV165" t="s">
+    <row r="163" spans="49:49">
+      <c r="AW163" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="166" spans="48:48">
-      <c r="AV166" t="s">
+    <row r="164" spans="49:49">
+      <c r="AW164" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="167" spans="48:48">
-      <c r="AV167" t="s">
+    <row r="165" spans="49:49">
+      <c r="AW165" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="168" spans="48:48">
-      <c r="AV168" t="s">
+    <row r="166" spans="49:49">
+      <c r="AW166" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="169" spans="48:48">
-      <c r="AV169" t="s">
+    <row r="167" spans="49:49">
+      <c r="AW167" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="170" spans="48:48">
-      <c r="AV170" t="s">
+    <row r="168" spans="49:49">
+      <c r="AW168" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="171" spans="48:48">
-      <c r="AV171" t="s">
+    <row r="169" spans="49:49">
+      <c r="AW169" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="172" spans="48:48">
-      <c r="AV172" t="s">
+    <row r="170" spans="49:49">
+      <c r="AW170" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="173" spans="48:48">
-      <c r="AV173" t="s">
+    <row r="171" spans="49:49">
+      <c r="AW171" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="174" spans="48:48">
-      <c r="AV174" t="s">
+    <row r="172" spans="49:49">
+      <c r="AW172" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="175" spans="48:48">
-      <c r="AV175" t="s">
+    <row r="173" spans="49:49">
+      <c r="AW173" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="176" spans="48:48">
-      <c r="AV176" t="s">
+    <row r="174" spans="49:49">
+      <c r="AW174" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="177" spans="48:48">
-      <c r="AV177" t="s">
+    <row r="175" spans="49:49">
+      <c r="AW175" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="178" spans="48:48">
-      <c r="AV178" t="s">
+    <row r="176" spans="49:49">
+      <c r="AW176" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="179" spans="48:48">
-      <c r="AV179" t="s">
+    <row r="177" spans="49:49">
+      <c r="AW177" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="180" spans="48:48">
-      <c r="AV180" t="s">
+    <row r="178" spans="49:49">
+      <c r="AW178" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="181" spans="48:48">
-      <c r="AV181" t="s">
+    <row r="179" spans="49:49">
+      <c r="AW179" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="182" spans="48:48">
-      <c r="AV182" t="s">
+    <row r="180" spans="49:49">
+      <c r="AW180" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="183" spans="48:48">
-      <c r="AV183" t="s">
+    <row r="181" spans="49:49">
+      <c r="AW181" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="184" spans="48:48">
-      <c r="AV184" t="s">
+    <row r="182" spans="49:49">
+      <c r="AW182" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="185" spans="48:48">
-      <c r="AV185" t="s">
+    <row r="183" spans="49:49">
+      <c r="AW183" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="186" spans="48:48">
-      <c r="AV186" t="s">
+    <row r="184" spans="49:49">
+      <c r="AW184" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="187" spans="48:48">
-      <c r="AV187" t="s">
+    <row r="185" spans="49:49">
+      <c r="AW185" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="188" spans="48:48">
-      <c r="AV188" t="s">
+    <row r="186" spans="49:49">
+      <c r="AW186" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="189" spans="48:48">
-      <c r="AV189" t="s">
+    <row r="187" spans="49:49">
+      <c r="AW187" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="190" spans="48:48">
-      <c r="AV190" t="s">
+    <row r="188" spans="49:49">
+      <c r="AW188" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="191" spans="48:48">
-      <c r="AV191" t="s">
+    <row r="189" spans="49:49">
+      <c r="AW189" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="192" spans="48:48">
-      <c r="AV192" t="s">
+    <row r="190" spans="49:49">
+      <c r="AW190" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="193" spans="48:48">
-      <c r="AV193" t="s">
+    <row r="191" spans="49:49">
+      <c r="AW191" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="194" spans="48:48">
-      <c r="AV194" t="s">
+    <row r="192" spans="49:49">
+      <c r="AW192" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="195" spans="48:48">
-      <c r="AV195" t="s">
+    <row r="193" spans="49:49">
+      <c r="AW193" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="196" spans="48:48">
-      <c r="AV196" t="s">
+    <row r="194" spans="49:49">
+      <c r="AW194" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="197" spans="48:48">
-      <c r="AV197" t="s">
+    <row r="195" spans="49:49">
+      <c r="AW195" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="198" spans="48:48">
-      <c r="AV198" t="s">
+    <row r="196" spans="49:49">
+      <c r="AW196" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="199" spans="48:48">
-      <c r="AV199" t="s">
+    <row r="197" spans="49:49">
+      <c r="AW197" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="200" spans="48:48">
-      <c r="AV200" t="s">
+    <row r="198" spans="49:49">
+      <c r="AW198" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="201" spans="48:48">
-      <c r="AV201" t="s">
+    <row r="199" spans="49:49">
+      <c r="AW199" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="202" spans="48:48">
-      <c r="AV202" t="s">
+    <row r="200" spans="49:49">
+      <c r="AW200" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="203" spans="48:48">
-      <c r="AV203" t="s">
+    <row r="201" spans="49:49">
+      <c r="AW201" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="204" spans="48:48">
-      <c r="AV204" t="s">
+    <row r="202" spans="49:49">
+      <c r="AW202" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="205" spans="48:48">
-      <c r="AV205" t="s">
+    <row r="203" spans="49:49">
+      <c r="AW203" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="206" spans="48:48">
-      <c r="AV206" t="s">
+    <row r="204" spans="49:49">
+      <c r="AW204" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="207" spans="48:48">
-      <c r="AV207" t="s">
+    <row r="205" spans="49:49">
+      <c r="AW205" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="208" spans="48:48">
-      <c r="AV208" t="s">
+    <row r="206" spans="49:49">
+      <c r="AW206" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="209" spans="48:48">
-      <c r="AV209" t="s">
+    <row r="207" spans="49:49">
+      <c r="AW207" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="210" spans="48:48">
-      <c r="AV210" t="s">
+    <row r="208" spans="49:49">
+      <c r="AW208" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="211" spans="48:48">
-      <c r="AV211" t="s">
+    <row r="209" spans="49:49">
+      <c r="AW209" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="212" spans="48:48">
-      <c r="AV212" t="s">
+    <row r="210" spans="49:49">
+      <c r="AW210" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="213" spans="48:48">
-      <c r="AV213" t="s">
+    <row r="211" spans="49:49">
+      <c r="AW211" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="214" spans="48:48">
-      <c r="AV214" t="s">
+    <row r="212" spans="49:49">
+      <c r="AW212" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="215" spans="48:48">
-      <c r="AV215" t="s">
+    <row r="213" spans="49:49">
+      <c r="AW213" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="216" spans="48:48">
-      <c r="AV216" t="s">
+    <row r="214" spans="49:49">
+      <c r="AW214" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="217" spans="48:48">
-      <c r="AV217" t="s">
+    <row r="215" spans="49:49">
+      <c r="AW215" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="218" spans="48:48">
-      <c r="AV218" t="s">
+    <row r="216" spans="49:49">
+      <c r="AW216" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="219" spans="48:48">
-      <c r="AV219" t="s">
+    <row r="217" spans="49:49">
+      <c r="AW217" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="220" spans="48:48">
-      <c r="AV220" t="s">
+    <row r="218" spans="49:49">
+      <c r="AW218" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="221" spans="48:48">
-      <c r="AV221" t="s">
+    <row r="219" spans="49:49">
+      <c r="AW219" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="222" spans="48:48">
-      <c r="AV222" t="s">
+    <row r="220" spans="49:49">
+      <c r="AW220" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="223" spans="48:48">
-      <c r="AV223" t="s">
+    <row r="221" spans="49:49">
+      <c r="AW221" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="224" spans="48:48">
-      <c r="AV224" t="s">
+    <row r="222" spans="49:49">
+      <c r="AW222" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="225" spans="48:48">
-      <c r="AV225" t="s">
+    <row r="223" spans="49:49">
+      <c r="AW223" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="226" spans="48:48">
-      <c r="AV226" t="s">
+    <row r="224" spans="49:49">
+      <c r="AW224" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="227" spans="48:48">
-      <c r="AV227" t="s">
+    <row r="225" spans="49:49">
+      <c r="AW225" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="228" spans="48:48">
-      <c r="AV228" t="s">
+    <row r="226" spans="49:49">
+      <c r="AW226" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="229" spans="48:48">
-      <c r="AV229" t="s">
+    <row r="227" spans="49:49">
+      <c r="AW227" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="230" spans="48:48">
-      <c r="AV230" t="s">
+    <row r="228" spans="49:49">
+      <c r="AW228" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="231" spans="48:48">
-      <c r="AV231" t="s">
+    <row r="229" spans="49:49">
+      <c r="AW229" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="232" spans="48:48">
-      <c r="AV232" t="s">
+    <row r="230" spans="49:49">
+      <c r="AW230" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="233" spans="48:48">
-      <c r="AV233" t="s">
+    <row r="231" spans="49:49">
+      <c r="AW231" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="234" spans="48:48">
-      <c r="AV234" t="s">
+    <row r="232" spans="49:49">
+      <c r="AW232" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="235" spans="48:48">
-      <c r="AV235" t="s">
+    <row r="233" spans="49:49">
+      <c r="AW233" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="236" spans="48:48">
-      <c r="AV236" t="s">
+    <row r="234" spans="49:49">
+      <c r="AW234" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="237" spans="48:48">
-      <c r="AV237" t="s">
+    <row r="235" spans="49:49">
+      <c r="AW235" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="238" spans="48:48">
-      <c r="AV238" t="s">
+    <row r="236" spans="49:49">
+      <c r="AW236" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="239" spans="48:48">
-      <c r="AV239" t="s">
+    <row r="237" spans="49:49">
+      <c r="AW237" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="240" spans="48:48">
-      <c r="AV240" t="s">
+    <row r="238" spans="49:49">
+      <c r="AW238" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="241" spans="48:48">
-      <c r="AV241" t="s">
+    <row r="239" spans="49:49">
+      <c r="AW239" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="242" spans="48:48">
-      <c r="AV242" t="s">
+    <row r="240" spans="49:49">
+      <c r="AW240" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="243" spans="48:48">
-      <c r="AV243" t="s">
+    <row r="241" spans="49:49">
+      <c r="AW241" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="244" spans="48:48">
-      <c r="AV244" t="s">
+    <row r="242" spans="49:49">
+      <c r="AW242" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="245" spans="48:48">
-      <c r="AV245" t="s">
+    <row r="243" spans="49:49">
+      <c r="AW243" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="246" spans="48:48">
-      <c r="AV246" t="s">
+    <row r="244" spans="49:49">
+      <c r="AW244" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="247" spans="48:48">
-      <c r="AV247" t="s">
+    <row r="245" spans="49:49">
+      <c r="AW245" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="248" spans="48:48">
-      <c r="AV248" t="s">
+    <row r="246" spans="49:49">
+      <c r="AW246" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="249" spans="48:48">
-      <c r="AV249" t="s">
+    <row r="247" spans="49:49">
+      <c r="AW247" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="250" spans="48:48">
-      <c r="AV250" t="s">
+    <row r="248" spans="49:49">
+      <c r="AW248" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="251" spans="48:48">
-      <c r="AV251" t="s">
+    <row r="249" spans="49:49">
+      <c r="AW249" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="252" spans="48:48">
-      <c r="AV252" t="s">
+    <row r="250" spans="49:49">
+      <c r="AW250" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="253" spans="48:48">
-      <c r="AV253" t="s">
+    <row r="251" spans="49:49">
+      <c r="AW251" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="254" spans="48:48">
-      <c r="AV254" t="s">
+    <row r="252" spans="49:49">
+      <c r="AW252" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="255" spans="48:48">
-      <c r="AV255" t="s">
+    <row r="253" spans="49:49">
+      <c r="AW253" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="256" spans="48:48">
-      <c r="AV256" t="s">
+    <row r="254" spans="49:49">
+      <c r="AW254" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="257" spans="48:48">
-      <c r="AV257" t="s">
+    <row r="255" spans="49:49">
+      <c r="AW255" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="258" spans="48:48">
-      <c r="AV258" t="s">
+    <row r="256" spans="49:49">
+      <c r="AW256" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="259" spans="48:48">
-      <c r="AV259" t="s">
+    <row r="257" spans="49:49">
+      <c r="AW257" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="260" spans="48:48">
-      <c r="AV260" t="s">
+    <row r="258" spans="49:49">
+      <c r="AW258" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="261" spans="48:48">
-      <c r="AV261" t="s">
+    <row r="259" spans="49:49">
+      <c r="AW259" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="262" spans="48:48">
-      <c r="AV262" t="s">
+    <row r="260" spans="49:49">
+      <c r="AW260" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="263" spans="48:48">
-      <c r="AV263" t="s">
+    <row r="261" spans="49:49">
+      <c r="AW261" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="264" spans="48:48">
-      <c r="AV264" t="s">
+    <row r="262" spans="49:49">
+      <c r="AW262" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="265" spans="48:48">
-      <c r="AV265" t="s">
+    <row r="263" spans="49:49">
+      <c r="AW263" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="266" spans="48:48">
-      <c r="AV266" t="s">
+    <row r="264" spans="49:49">
+      <c r="AW264" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="267" spans="48:48">
-      <c r="AV267" t="s">
+    <row r="265" spans="49:49">
+      <c r="AW265" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="268" spans="48:48">
-      <c r="AV268" t="s">
+    <row r="266" spans="49:49">
+      <c r="AW266" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="269" spans="48:48">
-      <c r="AV269" t="s">
+    <row r="267" spans="49:49">
+      <c r="AW267" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="270" spans="48:48">
-      <c r="AV270" t="s">
+    <row r="268" spans="49:49">
+      <c r="AW268" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="271" spans="48:48">
-      <c r="AV271" t="s">
+    <row r="269" spans="49:49">
+      <c r="AW269" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="272" spans="48:48">
-      <c r="AV272" t="s">
+    <row r="270" spans="49:49">
+      <c r="AW270" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="273" spans="48:48">
-      <c r="AV273" t="s">
+    <row r="271" spans="49:49">
+      <c r="AW271" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="274" spans="48:48">
-      <c r="AV274" t="s">
+    <row r="272" spans="49:49">
+      <c r="AW272" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="275" spans="48:48">
-      <c r="AV275" t="s">
+    <row r="273" spans="49:49">
+      <c r="AW273" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="276" spans="48:48">
-      <c r="AV276" t="s">
+    <row r="274" spans="49:49">
+      <c r="AW274" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="277" spans="48:48">
-      <c r="AV277" t="s">
+    <row r="275" spans="49:49">
+      <c r="AW275" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="278" spans="48:48">
-      <c r="AV278" t="s">
+    <row r="276" spans="49:49">
+      <c r="AW276" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="279" spans="48:48">
-      <c r="AV279" t="s">
+    <row r="277" spans="49:49">
+      <c r="AW277" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="280" spans="48:48">
-      <c r="AV280" t="s">
+    <row r="278" spans="49:49">
+      <c r="AW278" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="281" spans="48:48">
-      <c r="AV281" t="s">
+    <row r="279" spans="49:49">
+      <c r="AW279" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="282" spans="48:48">
-      <c r="AV282" t="s">
+    <row r="280" spans="49:49">
+      <c r="AW280" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="283" spans="48:48">
-      <c r="AV283" t="s">
+    <row r="281" spans="49:49">
+      <c r="AW281" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="284" spans="48:48">
-      <c r="AV284" t="s">
+    <row r="282" spans="49:49">
+      <c r="AW282" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="285" spans="48:48">
-      <c r="AV285" t="s">
+    <row r="283" spans="49:49">
+      <c r="AW283" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="286" spans="48:48">
-      <c r="AV286" t="s">
+    <row r="284" spans="49:49">
+      <c r="AW284" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="287" spans="48:48">
-      <c r="AV287" t="s">
+    <row r="285" spans="49:49">
+      <c r="AW285" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="288" spans="48:48">
-      <c r="AV288" t="s">
+    <row r="286" spans="49:49">
+      <c r="AW286" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="289" spans="48:48">
-      <c r="AV289" t="s">
+    <row r="287" spans="49:49">
+      <c r="AW287" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="290" spans="48:48">
-      <c r="AV290" t="s">
+    <row r="288" spans="49:49">
+      <c r="AW288" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="291" spans="48:48">
-      <c r="AV291" t="s">
+    <row r="289" spans="49:49">
+      <c r="AW289" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="292" spans="48:48">
-      <c r="AV292" t="s">
+    <row r="290" spans="49:49">
+      <c r="AW290" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="293" spans="48:48">
-      <c r="AV293" t="s">
+    <row r="291" spans="49:49">
+      <c r="AW291" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="294" spans="48:48">
-      <c r="AV294" t="s">
+    <row r="292" spans="49:49">
+      <c r="AW292" t="s">
         <v>699</v>
+      </c>
+    </row>
+    <row r="293" spans="49:49">
+      <c r="AW293" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="294" spans="49:49">
+      <c r="AW294" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000027/metadata_template_ERC000027.xlsx
+++ b/templates/ERC000027/metadata_template_ERC000027.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="environmentalpackage">'cv_sample'!$AI$1:$AI$1</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$M$1:$M$5</definedName>
     <definedName name="oxygenationstatusofsample">'cv_sample'!$T$1:$T$2</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$O$1:$O$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$AE$1:$AE$3</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="888">
   <si>
     <t>alias</t>
   </si>
@@ -454,6 +454,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -544,6 +547,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1471,9 +1477,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1492,6 +1495,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1693,6 +1699,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1702,9 +1711,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1744,7 +1750,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1813,6 +1819,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1888,6 +1897,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1909,6 +1921,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1954,6 +1969,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1966,6 +1984,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1975,9 +1996,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2002,6 +2020,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2062,10 +2083,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -3207,10 +3228,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3251,10 +3272,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3281,7 +3302,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3298,7 +3319,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -3315,7 +3336,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -3332,7 +3353,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3349,7 +3370,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3366,7 +3387,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3383,7 +3404,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3400,7 +3421,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3417,7 +3438,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3434,7 +3455,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3448,7 +3469,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3462,7 +3483,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3476,7 +3497,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3490,7 +3511,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3504,7 +3525,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3518,7 +3539,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3532,7 +3553,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3546,7 +3567,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3556,8 +3577,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3568,7 +3592,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3579,7 +3603,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3590,7 +3614,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3601,7 +3625,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3612,7 +3636,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3623,7 +3647,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3634,7 +3658,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3645,7 +3669,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3656,7 +3680,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3667,7 +3691,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3678,7 +3702,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3689,7 +3713,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3700,7 +3724,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3708,7 +3732,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3716,7 +3740,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3724,7 +3748,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3732,7 +3756,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3740,7 +3764,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3748,7 +3772,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3756,7 +3780,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3764,7 +3788,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3772,7 +3796,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3780,236 +3804,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4031,27 +4060,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4071,122 +4100,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4210,840 +4239,840 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:140" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -5079,1602 +5108,1627 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="L1:BJ289"/>
+  <dimension ref="L1:BJ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="12:62">
       <c r="L1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AI1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AW1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BJ1" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="2" spans="12:62">
       <c r="L2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="T2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AE2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AW2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BJ2" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="12:62">
       <c r="L3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AE3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AW3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="12:62">
       <c r="L4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AW4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="12:62">
       <c r="L5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AW5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="12:62">
       <c r="L6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AW6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="12:62">
       <c r="L7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AW7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="12:62">
       <c r="L8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AW8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="12:62">
       <c r="L9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AW9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="12:62">
       <c r="L10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AW10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="12:62">
       <c r="L11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AW11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="12:62">
       <c r="L12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AW12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="12:62">
       <c r="L13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AW13" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="12:62">
       <c r="L14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AW14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="12:62">
       <c r="L15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AW15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="12:62">
       <c r="L16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AW16" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="12:49">
       <c r="L17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AW17" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="12:49">
       <c r="L18" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AW18" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="12:49">
       <c r="L19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AW19" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="12:49">
       <c r="L20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AW20" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="12:49">
       <c r="L21" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AW21" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="12:49">
       <c r="L22" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AW22" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="12:49">
       <c r="L23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AW23" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="12:49">
       <c r="L24" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AW24" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="12:49">
       <c r="L25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AW25" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="12:49">
       <c r="L26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AW26" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="12:49">
       <c r="L27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AW27" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="12:49">
       <c r="L28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AW28" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="12:49">
       <c r="L29" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AW29" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="12:49">
       <c r="L30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AW30" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="12:49">
       <c r="AW31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="12:49">
       <c r="AW32" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" spans="49:49">
       <c r="AW33" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="49:49">
       <c r="AW34" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" spans="49:49">
       <c r="AW35" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="49:49">
       <c r="AW36" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="49:49">
       <c r="AW37" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" spans="49:49">
       <c r="AW38" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" spans="49:49">
       <c r="AW39" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="49:49">
       <c r="AW40" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="49:49">
       <c r="AW41" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42" spans="49:49">
       <c r="AW42" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" spans="49:49">
       <c r="AW43" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="49:49">
       <c r="AW44" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="49:49">
       <c r="AW45" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="49:49">
       <c r="AW46" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47" spans="49:49">
       <c r="AW47" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="48" spans="49:49">
       <c r="AW48" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="49" spans="49:49">
       <c r="AW49" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="50" spans="49:49">
       <c r="AW50" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="51" spans="49:49">
       <c r="AW51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="52" spans="49:49">
       <c r="AW52" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="53" spans="49:49">
       <c r="AW53" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="49:49">
       <c r="AW54" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="55" spans="49:49">
       <c r="AW55" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="56" spans="49:49">
       <c r="AW56" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57" spans="49:49">
       <c r="AW57" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="49:49">
       <c r="AW58" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="59" spans="49:49">
       <c r="AW59" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="60" spans="49:49">
       <c r="AW60" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61" spans="49:49">
       <c r="AW61" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" spans="49:49">
       <c r="AW62" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="63" spans="49:49">
       <c r="AW63" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" spans="49:49">
       <c r="AW64" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="49:49">
       <c r="AW65" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="66" spans="49:49">
       <c r="AW66" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="67" spans="49:49">
       <c r="AW67" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" spans="49:49">
       <c r="AW68" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="69" spans="49:49">
       <c r="AW69" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70" spans="49:49">
       <c r="AW70" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="71" spans="49:49">
       <c r="AW71" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" spans="49:49">
       <c r="AW72" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" spans="49:49">
       <c r="AW73" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74" spans="49:49">
       <c r="AW74" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="75" spans="49:49">
       <c r="AW75" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="76" spans="49:49">
       <c r="AW76" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="77" spans="49:49">
       <c r="AW77" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="78" spans="49:49">
       <c r="AW78" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="79" spans="49:49">
       <c r="AW79" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" spans="49:49">
       <c r="AW80" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" spans="49:49">
       <c r="AW81" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="49:49">
       <c r="AW82" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="83" spans="49:49">
       <c r="AW83" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="84" spans="49:49">
       <c r="AW84" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="85" spans="49:49">
       <c r="AW85" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="86" spans="49:49">
       <c r="AW86" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="87" spans="49:49">
       <c r="AW87" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="88" spans="49:49">
       <c r="AW88" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="89" spans="49:49">
       <c r="AW89" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="90" spans="49:49">
       <c r="AW90" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="91" spans="49:49">
       <c r="AW91" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92" spans="49:49">
       <c r="AW92" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" spans="49:49">
       <c r="AW93" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="49:49">
       <c r="AW94" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" spans="49:49">
       <c r="AW95" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96" spans="49:49">
       <c r="AW96" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="97" spans="49:49">
       <c r="AW97" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="98" spans="49:49">
       <c r="AW98" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="99" spans="49:49">
       <c r="AW99" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="49:49">
       <c r="AW100" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="101" spans="49:49">
       <c r="AW101" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="102" spans="49:49">
       <c r="AW102" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="103" spans="49:49">
       <c r="AW103" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="104" spans="49:49">
       <c r="AW104" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="105" spans="49:49">
       <c r="AW105" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="106" spans="49:49">
       <c r="AW106" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="107" spans="49:49">
       <c r="AW107" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="108" spans="49:49">
       <c r="AW108" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="109" spans="49:49">
       <c r="AW109" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="110" spans="49:49">
       <c r="AW110" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="111" spans="49:49">
       <c r="AW111" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="112" spans="49:49">
       <c r="AW112" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="113" spans="49:49">
       <c r="AW113" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="114" spans="49:49">
       <c r="AW114" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="115" spans="49:49">
       <c r="AW115" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="116" spans="49:49">
       <c r="AW116" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="117" spans="49:49">
       <c r="AW117" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="118" spans="49:49">
       <c r="AW118" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="119" spans="49:49">
       <c r="AW119" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="120" spans="49:49">
       <c r="AW120" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="121" spans="49:49">
       <c r="AW121" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="122" spans="49:49">
       <c r="AW122" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="123" spans="49:49">
       <c r="AW123" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="124" spans="49:49">
       <c r="AW124" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="125" spans="49:49">
       <c r="AW125" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="126" spans="49:49">
       <c r="AW126" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="127" spans="49:49">
       <c r="AW127" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="128" spans="49:49">
       <c r="AW128" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="129" spans="49:49">
       <c r="AW129" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="130" spans="49:49">
       <c r="AW130" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="131" spans="49:49">
       <c r="AW131" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="132" spans="49:49">
       <c r="AW132" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="133" spans="49:49">
       <c r="AW133" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="134" spans="49:49">
       <c r="AW134" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="135" spans="49:49">
       <c r="AW135" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="136" spans="49:49">
       <c r="AW136" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="137" spans="49:49">
       <c r="AW137" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="138" spans="49:49">
       <c r="AW138" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="49:49">
       <c r="AW139" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="140" spans="49:49">
       <c r="AW140" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="141" spans="49:49">
       <c r="AW141" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="142" spans="49:49">
       <c r="AW142" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="143" spans="49:49">
       <c r="AW143" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="144" spans="49:49">
       <c r="AW144" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="145" spans="49:49">
       <c r="AW145" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="146" spans="49:49">
       <c r="AW146" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="147" spans="49:49">
       <c r="AW147" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="148" spans="49:49">
       <c r="AW148" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="149" spans="49:49">
       <c r="AW149" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="150" spans="49:49">
       <c r="AW150" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="151" spans="49:49">
       <c r="AW151" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="152" spans="49:49">
       <c r="AW152" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="153" spans="49:49">
       <c r="AW153" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="154" spans="49:49">
       <c r="AW154" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="155" spans="49:49">
       <c r="AW155" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="156" spans="49:49">
       <c r="AW156" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="157" spans="49:49">
       <c r="AW157" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="158" spans="49:49">
       <c r="AW158" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="159" spans="49:49">
       <c r="AW159" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="160" spans="49:49">
       <c r="AW160" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="161" spans="49:49">
       <c r="AW161" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="162" spans="49:49">
       <c r="AW162" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="163" spans="49:49">
       <c r="AW163" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="164" spans="49:49">
       <c r="AW164" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="165" spans="49:49">
       <c r="AW165" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="166" spans="49:49">
       <c r="AW166" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="167" spans="49:49">
       <c r="AW167" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="168" spans="49:49">
       <c r="AW168" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="169" spans="49:49">
       <c r="AW169" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="170" spans="49:49">
       <c r="AW170" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="171" spans="49:49">
       <c r="AW171" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="172" spans="49:49">
       <c r="AW172" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="173" spans="49:49">
       <c r="AW173" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="174" spans="49:49">
       <c r="AW174" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="175" spans="49:49">
       <c r="AW175" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="176" spans="49:49">
       <c r="AW176" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="177" spans="49:49">
       <c r="AW177" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="178" spans="49:49">
       <c r="AW178" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="179" spans="49:49">
       <c r="AW179" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="180" spans="49:49">
       <c r="AW180" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="181" spans="49:49">
       <c r="AW181" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="182" spans="49:49">
       <c r="AW182" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="183" spans="49:49">
       <c r="AW183" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="184" spans="49:49">
       <c r="AW184" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="185" spans="49:49">
       <c r="AW185" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="186" spans="49:49">
       <c r="AW186" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="187" spans="49:49">
       <c r="AW187" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="188" spans="49:49">
       <c r="AW188" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="189" spans="49:49">
       <c r="AW189" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="190" spans="49:49">
       <c r="AW190" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="191" spans="49:49">
       <c r="AW191" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="192" spans="49:49">
       <c r="AW192" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="193" spans="49:49">
       <c r="AW193" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="194" spans="49:49">
       <c r="AW194" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="195" spans="49:49">
       <c r="AW195" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="196" spans="49:49">
       <c r="AW196" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="197" spans="49:49">
       <c r="AW197" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="198" spans="49:49">
       <c r="AW198" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="199" spans="49:49">
       <c r="AW199" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="200" spans="49:49">
       <c r="AW200" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="201" spans="49:49">
       <c r="AW201" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="202" spans="49:49">
       <c r="AW202" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="203" spans="49:49">
       <c r="AW203" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="204" spans="49:49">
       <c r="AW204" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="205" spans="49:49">
       <c r="AW205" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="206" spans="49:49">
       <c r="AW206" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="207" spans="49:49">
       <c r="AW207" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="208" spans="49:49">
       <c r="AW208" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="209" spans="49:49">
       <c r="AW209" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="210" spans="49:49">
       <c r="AW210" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="211" spans="49:49">
       <c r="AW211" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="212" spans="49:49">
       <c r="AW212" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="213" spans="49:49">
       <c r="AW213" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="214" spans="49:49">
       <c r="AW214" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="215" spans="49:49">
       <c r="AW215" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="216" spans="49:49">
       <c r="AW216" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="217" spans="49:49">
       <c r="AW217" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="218" spans="49:49">
       <c r="AW218" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="219" spans="49:49">
       <c r="AW219" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="220" spans="49:49">
       <c r="AW220" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="221" spans="49:49">
       <c r="AW221" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="222" spans="49:49">
       <c r="AW222" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="223" spans="49:49">
       <c r="AW223" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="224" spans="49:49">
       <c r="AW224" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="225" spans="49:49">
       <c r="AW225" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="226" spans="49:49">
       <c r="AW226" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="227" spans="49:49">
       <c r="AW227" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="228" spans="49:49">
       <c r="AW228" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="229" spans="49:49">
       <c r="AW229" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="230" spans="49:49">
       <c r="AW230" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="231" spans="49:49">
       <c r="AW231" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="232" spans="49:49">
       <c r="AW232" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="233" spans="49:49">
       <c r="AW233" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="234" spans="49:49">
       <c r="AW234" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="235" spans="49:49">
       <c r="AW235" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="236" spans="49:49">
       <c r="AW236" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="237" spans="49:49">
       <c r="AW237" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="238" spans="49:49">
       <c r="AW238" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="239" spans="49:49">
       <c r="AW239" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="240" spans="49:49">
       <c r="AW240" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="241" spans="49:49">
       <c r="AW241" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="242" spans="49:49">
       <c r="AW242" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="243" spans="49:49">
       <c r="AW243" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="244" spans="49:49">
       <c r="AW244" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="245" spans="49:49">
       <c r="AW245" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="246" spans="49:49">
       <c r="AW246" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="247" spans="49:49">
       <c r="AW247" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="248" spans="49:49">
       <c r="AW248" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="249" spans="49:49">
       <c r="AW249" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="250" spans="49:49">
       <c r="AW250" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="251" spans="49:49">
       <c r="AW251" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="252" spans="49:49">
       <c r="AW252" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="253" spans="49:49">
       <c r="AW253" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="254" spans="49:49">
       <c r="AW254" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="255" spans="49:49">
       <c r="AW255" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="256" spans="49:49">
       <c r="AW256" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="257" spans="49:49">
       <c r="AW257" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="258" spans="49:49">
       <c r="AW258" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="259" spans="49:49">
       <c r="AW259" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="260" spans="49:49">
       <c r="AW260" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="261" spans="49:49">
       <c r="AW261" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="262" spans="49:49">
       <c r="AW262" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="263" spans="49:49">
       <c r="AW263" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="264" spans="49:49">
       <c r="AW264" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="265" spans="49:49">
       <c r="AW265" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="266" spans="49:49">
       <c r="AW266" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="267" spans="49:49">
       <c r="AW267" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="268" spans="49:49">
       <c r="AW268" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="269" spans="49:49">
       <c r="AW269" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="270" spans="49:49">
       <c r="AW270" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="271" spans="49:49">
       <c r="AW271" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="272" spans="49:49">
       <c r="AW272" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="273" spans="49:49">
       <c r="AW273" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="274" spans="49:49">
       <c r="AW274" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="275" spans="49:49">
       <c r="AW275" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="276" spans="49:49">
       <c r="AW276" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="277" spans="49:49">
       <c r="AW277" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="278" spans="49:49">
       <c r="AW278" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="279" spans="49:49">
       <c r="AW279" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="280" spans="49:49">
       <c r="AW280" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="281" spans="49:49">
       <c r="AW281" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="282" spans="49:49">
       <c r="AW282" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="283" spans="49:49">
       <c r="AW283" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="284" spans="49:49">
       <c r="AW284" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="285" spans="49:49">
       <c r="AW285" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="286" spans="49:49">
       <c r="AW286" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="287" spans="49:49">
       <c r="AW287" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="288" spans="49:49">
       <c r="AW288" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="289" spans="49:49">
       <c r="AW289" t="s">
-        <v>694</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="290" spans="49:49">
+      <c r="AW290" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="291" spans="49:49">
+      <c r="AW291" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="292" spans="49:49">
+      <c r="AW292" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="293" spans="49:49">
+      <c r="AW293" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="294" spans="49:49">
+      <c r="AW294" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000027/metadata_template_ERC000027.xlsx
+++ b/templates/ERC000027/metadata_template_ERC000027.xlsx
@@ -20,7 +20,7 @@
     <definedName name="environmentalpackage">'cv_sample'!$AI$1:$AI$1</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="889">
   <si>
     <t>alias</t>
   </si>
@@ -734,6 +734,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -3231,7 +3234,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3275,7 +3278,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3302,7 +3305,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4039,6 +4042,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4060,27 +4068,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4100,122 +4108,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4239,840 +4247,840 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:140" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
   </sheetData>
@@ -5113,1622 +5121,1622 @@
   <sheetData>
     <row r="1" spans="12:62">
       <c r="L1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AE1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AI1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AW1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="BJ1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2" spans="12:62">
       <c r="L2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AE2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AW2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="BJ2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3" spans="12:62">
       <c r="L3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AE3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AW3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="12:62">
       <c r="L4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AW4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="12:62">
       <c r="L5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AW5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="12:62">
       <c r="L6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AW6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="12:62">
       <c r="L7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AW7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="12:62">
       <c r="L8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AW8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="12:62">
       <c r="L9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AW9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="12:62">
       <c r="L10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AW10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="12:62">
       <c r="L11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AW11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="12:62">
       <c r="L12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AW12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="12:62">
       <c r="L13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AW13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="12:62">
       <c r="L14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AW14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="12:62">
       <c r="L15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AW15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="12:62">
       <c r="L16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AW16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="12:49">
       <c r="L17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AW17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="12:49">
       <c r="L18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AW18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="12:49">
       <c r="L19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AW19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="12:49">
       <c r="L20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AW20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="12:49">
       <c r="L21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AW21" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="12:49">
       <c r="L22" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AW22" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="12:49">
       <c r="L23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AW23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" spans="12:49">
       <c r="L24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AW24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="12:49">
       <c r="L25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AW25" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="12:49">
       <c r="L26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AW26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="12:49">
       <c r="L27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AW27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" spans="12:49">
       <c r="L28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AW28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="29" spans="12:49">
       <c r="L29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AW29" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="12:49">
       <c r="L30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AW30" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="12:49">
       <c r="AW31" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="12:49">
       <c r="AW32" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="49:49">
       <c r="AW33" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="49:49">
       <c r="AW34" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="49:49">
       <c r="AW35" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="49:49">
       <c r="AW36" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37" spans="49:49">
       <c r="AW37" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="38" spans="49:49">
       <c r="AW38" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" spans="49:49">
       <c r="AW39" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="49:49">
       <c r="AW40" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="49:49">
       <c r="AW41" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="49:49">
       <c r="AW42" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43" spans="49:49">
       <c r="AW43" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="49:49">
       <c r="AW44" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="49:49">
       <c r="AW45" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" spans="49:49">
       <c r="AW46" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="49:49">
       <c r="AW47" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" spans="49:49">
       <c r="AW48" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="49" spans="49:49">
       <c r="AW49" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="50" spans="49:49">
       <c r="AW50" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" spans="49:49">
       <c r="AW51" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="52" spans="49:49">
       <c r="AW52" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" spans="49:49">
       <c r="AW53" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54" spans="49:49">
       <c r="AW54" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" spans="49:49">
       <c r="AW55" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="49:49">
       <c r="AW56" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="49:49">
       <c r="AW57" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="58" spans="49:49">
       <c r="AW58" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="59" spans="49:49">
       <c r="AW59" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60" spans="49:49">
       <c r="AW60" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61" spans="49:49">
       <c r="AW61" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="62" spans="49:49">
       <c r="AW62" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="63" spans="49:49">
       <c r="AW63" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="64" spans="49:49">
       <c r="AW64" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="65" spans="49:49">
       <c r="AW65" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="49:49">
       <c r="AW66" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="67" spans="49:49">
       <c r="AW67" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="68" spans="49:49">
       <c r="AW68" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="49:49">
       <c r="AW69" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="70" spans="49:49">
       <c r="AW70" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="71" spans="49:49">
       <c r="AW71" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="72" spans="49:49">
       <c r="AW72" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73" spans="49:49">
       <c r="AW73" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="74" spans="49:49">
       <c r="AW74" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="75" spans="49:49">
       <c r="AW75" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" spans="49:49">
       <c r="AW76" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" spans="49:49">
       <c r="AW77" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="78" spans="49:49">
       <c r="AW78" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="79" spans="49:49">
       <c r="AW79" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="80" spans="49:49">
       <c r="AW80" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="81" spans="49:49">
       <c r="AW81" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="82" spans="49:49">
       <c r="AW82" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="83" spans="49:49">
       <c r="AW83" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="84" spans="49:49">
       <c r="AW84" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="85" spans="49:49">
       <c r="AW85" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="86" spans="49:49">
       <c r="AW86" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="87" spans="49:49">
       <c r="AW87" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="88" spans="49:49">
       <c r="AW88" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="89" spans="49:49">
       <c r="AW89" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="90" spans="49:49">
       <c r="AW90" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="91" spans="49:49">
       <c r="AW91" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="92" spans="49:49">
       <c r="AW92" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93" spans="49:49">
       <c r="AW93" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="94" spans="49:49">
       <c r="AW94" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="95" spans="49:49">
       <c r="AW95" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="96" spans="49:49">
       <c r="AW96" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="97" spans="49:49">
       <c r="AW97" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="98" spans="49:49">
       <c r="AW98" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="99" spans="49:49">
       <c r="AW99" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="100" spans="49:49">
       <c r="AW100" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="101" spans="49:49">
       <c r="AW101" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="102" spans="49:49">
       <c r="AW102" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="103" spans="49:49">
       <c r="AW103" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="104" spans="49:49">
       <c r="AW104" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="105" spans="49:49">
       <c r="AW105" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="106" spans="49:49">
       <c r="AW106" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="107" spans="49:49">
       <c r="AW107" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="108" spans="49:49">
       <c r="AW108" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="109" spans="49:49">
       <c r="AW109" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="110" spans="49:49">
       <c r="AW110" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="111" spans="49:49">
       <c r="AW111" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="112" spans="49:49">
       <c r="AW112" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="113" spans="49:49">
       <c r="AW113" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="114" spans="49:49">
       <c r="AW114" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="115" spans="49:49">
       <c r="AW115" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="116" spans="49:49">
       <c r="AW116" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="117" spans="49:49">
       <c r="AW117" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="118" spans="49:49">
       <c r="AW118" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="119" spans="49:49">
       <c r="AW119" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="120" spans="49:49">
       <c r="AW120" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="121" spans="49:49">
       <c r="AW121" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="122" spans="49:49">
       <c r="AW122" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="123" spans="49:49">
       <c r="AW123" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="124" spans="49:49">
       <c r="AW124" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="125" spans="49:49">
       <c r="AW125" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="126" spans="49:49">
       <c r="AW126" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="127" spans="49:49">
       <c r="AW127" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="128" spans="49:49">
       <c r="AW128" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="129" spans="49:49">
       <c r="AW129" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="130" spans="49:49">
       <c r="AW130" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="131" spans="49:49">
       <c r="AW131" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="132" spans="49:49">
       <c r="AW132" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="133" spans="49:49">
       <c r="AW133" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="134" spans="49:49">
       <c r="AW134" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="135" spans="49:49">
       <c r="AW135" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="136" spans="49:49">
       <c r="AW136" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="137" spans="49:49">
       <c r="AW137" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="138" spans="49:49">
       <c r="AW138" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="139" spans="49:49">
       <c r="AW139" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="140" spans="49:49">
       <c r="AW140" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="141" spans="49:49">
       <c r="AW141" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="142" spans="49:49">
       <c r="AW142" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="143" spans="49:49">
       <c r="AW143" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="144" spans="49:49">
       <c r="AW144" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="145" spans="49:49">
       <c r="AW145" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="146" spans="49:49">
       <c r="AW146" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="147" spans="49:49">
       <c r="AW147" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="148" spans="49:49">
       <c r="AW148" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="149" spans="49:49">
       <c r="AW149" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="150" spans="49:49">
       <c r="AW150" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="151" spans="49:49">
       <c r="AW151" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="152" spans="49:49">
       <c r="AW152" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="153" spans="49:49">
       <c r="AW153" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="154" spans="49:49">
       <c r="AW154" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="155" spans="49:49">
       <c r="AW155" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="156" spans="49:49">
       <c r="AW156" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="157" spans="49:49">
       <c r="AW157" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="158" spans="49:49">
       <c r="AW158" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="159" spans="49:49">
       <c r="AW159" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="160" spans="49:49">
       <c r="AW160" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="161" spans="49:49">
       <c r="AW161" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="162" spans="49:49">
       <c r="AW162" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="163" spans="49:49">
       <c r="AW163" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="164" spans="49:49">
       <c r="AW164" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="165" spans="49:49">
       <c r="AW165" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="166" spans="49:49">
       <c r="AW166" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="167" spans="49:49">
       <c r="AW167" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="168" spans="49:49">
       <c r="AW168" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="169" spans="49:49">
       <c r="AW169" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="170" spans="49:49">
       <c r="AW170" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="171" spans="49:49">
       <c r="AW171" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="172" spans="49:49">
       <c r="AW172" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="173" spans="49:49">
       <c r="AW173" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="174" spans="49:49">
       <c r="AW174" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="175" spans="49:49">
       <c r="AW175" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="176" spans="49:49">
       <c r="AW176" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="177" spans="49:49">
       <c r="AW177" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="178" spans="49:49">
       <c r="AW178" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="179" spans="49:49">
       <c r="AW179" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="180" spans="49:49">
       <c r="AW180" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="181" spans="49:49">
       <c r="AW181" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="182" spans="49:49">
       <c r="AW182" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="183" spans="49:49">
       <c r="AW183" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="184" spans="49:49">
       <c r="AW184" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="185" spans="49:49">
       <c r="AW185" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="186" spans="49:49">
       <c r="AW186" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="187" spans="49:49">
       <c r="AW187" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="188" spans="49:49">
       <c r="AW188" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="189" spans="49:49">
       <c r="AW189" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="190" spans="49:49">
       <c r="AW190" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="191" spans="49:49">
       <c r="AW191" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="192" spans="49:49">
       <c r="AW192" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="193" spans="49:49">
       <c r="AW193" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="194" spans="49:49">
       <c r="AW194" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="195" spans="49:49">
       <c r="AW195" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="196" spans="49:49">
       <c r="AW196" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="197" spans="49:49">
       <c r="AW197" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="198" spans="49:49">
       <c r="AW198" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="199" spans="49:49">
       <c r="AW199" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="200" spans="49:49">
       <c r="AW200" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="201" spans="49:49">
       <c r="AW201" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="202" spans="49:49">
       <c r="AW202" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="203" spans="49:49">
       <c r="AW203" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="204" spans="49:49">
       <c r="AW204" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="205" spans="49:49">
       <c r="AW205" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="206" spans="49:49">
       <c r="AW206" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="207" spans="49:49">
       <c r="AW207" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="208" spans="49:49">
       <c r="AW208" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="209" spans="49:49">
       <c r="AW209" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="210" spans="49:49">
       <c r="AW210" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="211" spans="49:49">
       <c r="AW211" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="212" spans="49:49">
       <c r="AW212" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="213" spans="49:49">
       <c r="AW213" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="214" spans="49:49">
       <c r="AW214" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="215" spans="49:49">
       <c r="AW215" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="216" spans="49:49">
       <c r="AW216" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="217" spans="49:49">
       <c r="AW217" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="218" spans="49:49">
       <c r="AW218" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="219" spans="49:49">
       <c r="AW219" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="220" spans="49:49">
       <c r="AW220" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="221" spans="49:49">
       <c r="AW221" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="222" spans="49:49">
       <c r="AW222" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="223" spans="49:49">
       <c r="AW223" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="224" spans="49:49">
       <c r="AW224" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="225" spans="49:49">
       <c r="AW225" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="226" spans="49:49">
       <c r="AW226" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="227" spans="49:49">
       <c r="AW227" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="228" spans="49:49">
       <c r="AW228" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="229" spans="49:49">
       <c r="AW229" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="230" spans="49:49">
       <c r="AW230" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="231" spans="49:49">
       <c r="AW231" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="232" spans="49:49">
       <c r="AW232" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="233" spans="49:49">
       <c r="AW233" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="234" spans="49:49">
       <c r="AW234" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="235" spans="49:49">
       <c r="AW235" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="236" spans="49:49">
       <c r="AW236" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="237" spans="49:49">
       <c r="AW237" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="238" spans="49:49">
       <c r="AW238" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="239" spans="49:49">
       <c r="AW239" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="240" spans="49:49">
       <c r="AW240" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="241" spans="49:49">
       <c r="AW241" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="242" spans="49:49">
       <c r="AW242" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="243" spans="49:49">
       <c r="AW243" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="244" spans="49:49">
       <c r="AW244" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="245" spans="49:49">
       <c r="AW245" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="246" spans="49:49">
       <c r="AW246" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="247" spans="49:49">
       <c r="AW247" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="248" spans="49:49">
       <c r="AW248" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="249" spans="49:49">
       <c r="AW249" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="250" spans="49:49">
       <c r="AW250" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="251" spans="49:49">
       <c r="AW251" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="252" spans="49:49">
       <c r="AW252" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="253" spans="49:49">
       <c r="AW253" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="254" spans="49:49">
       <c r="AW254" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="255" spans="49:49">
       <c r="AW255" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="256" spans="49:49">
       <c r="AW256" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="257" spans="49:49">
       <c r="AW257" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="258" spans="49:49">
       <c r="AW258" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="259" spans="49:49">
       <c r="AW259" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="260" spans="49:49">
       <c r="AW260" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="261" spans="49:49">
       <c r="AW261" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="262" spans="49:49">
       <c r="AW262" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="263" spans="49:49">
       <c r="AW263" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="264" spans="49:49">
       <c r="AW264" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="265" spans="49:49">
       <c r="AW265" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="266" spans="49:49">
       <c r="AW266" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="267" spans="49:49">
       <c r="AW267" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="268" spans="49:49">
       <c r="AW268" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="269" spans="49:49">
       <c r="AW269" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="270" spans="49:49">
       <c r="AW270" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="271" spans="49:49">
       <c r="AW271" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="272" spans="49:49">
       <c r="AW272" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="273" spans="49:49">
       <c r="AW273" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="274" spans="49:49">
       <c r="AW274" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="275" spans="49:49">
       <c r="AW275" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="276" spans="49:49">
       <c r="AW276" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="277" spans="49:49">
       <c r="AW277" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="278" spans="49:49">
       <c r="AW278" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="279" spans="49:49">
       <c r="AW279" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="280" spans="49:49">
       <c r="AW280" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="281" spans="49:49">
       <c r="AW281" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="282" spans="49:49">
       <c r="AW282" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="283" spans="49:49">
       <c r="AW283" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="284" spans="49:49">
       <c r="AW284" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="285" spans="49:49">
       <c r="AW285" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="286" spans="49:49">
       <c r="AW286" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="287" spans="49:49">
       <c r="AW287" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="288" spans="49:49">
       <c r="AW288" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="289" spans="49:49">
       <c r="AW289" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="290" spans="49:49">
       <c r="AW290" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="291" spans="49:49">
       <c r="AW291" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="292" spans="49:49">
       <c r="AW292" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="293" spans="49:49">
       <c r="AW293" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="294" spans="49:49">
       <c r="AW294" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
